--- a/modules/resource_recommendation/data/Gampaha_DS_Flood_Emergency_Relief_2019_2025.xlsx
+++ b/modules/resource_recommendation/data/Gampaha_DS_Flood_Emergency_Relief_2019_2025.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lap.lk\Desktop\UOM\Year 4\Sem 1\Research\Flood-Relief-Mapping\Relief-Recommendation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lap.lk\Desktop\UOM\Year 4\Sem 1\Research\Flood-Relief-Mapping\modules\resource_recommendation\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17AE0080-FBB7-4E1F-817C-535843C0AB21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBED9D2B-B87B-4BA7-88BD-2825B35DD629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="51">
   <si>
     <t>Year</t>
   </si>
@@ -175,6 +175,9 @@
   </si>
   <si>
     <t>The relevant Regional Health Officer of the Department of Health should be informed regarding the supply of infant milk powder in case of emergency.</t>
+  </si>
+  <si>
+    <t>Female %</t>
   </si>
 </sst>
 </file>
@@ -628,28 +631,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q118"/>
+  <dimension ref="A1:R118"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.21875" customWidth="1"/>
     <col min="2" max="3" width="14.109375" customWidth="1"/>
     <col min="4" max="4" width="19.5546875" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="10.88671875" customWidth="1"/>
-    <col min="7" max="7" width="17.88671875" customWidth="1"/>
-    <col min="8" max="8" width="16.5546875" customWidth="1"/>
-    <col min="9" max="9" width="18.33203125" customWidth="1"/>
-    <col min="10" max="10" width="23" customWidth="1"/>
-    <col min="11" max="11" width="15.6640625" customWidth="1"/>
-    <col min="12" max="12" width="13.44140625" customWidth="1"/>
-    <col min="13" max="13" width="18.77734375" customWidth="1"/>
-    <col min="14" max="14" width="10.6640625" customWidth="1"/>
-    <col min="15" max="15" width="11.33203125" customWidth="1"/>
-    <col min="16" max="16" width="13.109375" customWidth="1"/>
-    <col min="17" max="17" width="12.5546875" customWidth="1"/>
+    <col min="6" max="7" width="10.88671875" customWidth="1"/>
+    <col min="8" max="8" width="17.88671875" customWidth="1"/>
+    <col min="9" max="9" width="16.5546875" customWidth="1"/>
+    <col min="10" max="10" width="18.33203125" customWidth="1"/>
+    <col min="11" max="11" width="23" customWidth="1"/>
+    <col min="12" max="12" width="15.6640625" customWidth="1"/>
+    <col min="13" max="13" width="13.44140625" customWidth="1"/>
+    <col min="14" max="14" width="18.77734375" customWidth="1"/>
+    <col min="15" max="15" width="10.6640625" customWidth="1"/>
+    <col min="16" max="16" width="11.33203125" customWidth="1"/>
+    <col min="17" max="17" width="13.109375" customWidth="1"/>
+    <col min="18" max="18" width="12.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="4" customFormat="1" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="4" customFormat="1" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>8</v>
       </c>
@@ -669,8 +672,9 @@
       <c r="O1" s="5"/>
       <c r="P1" s="5"/>
       <c r="Q1" s="5"/>
-    </row>
-    <row r="2" spans="1:17" s="3" customFormat="1" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R1" s="5"/>
+    </row>
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -690,40 +694,43 @@
         <v>45</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="7">
         <v>2019</v>
       </c>
@@ -743,31 +750,31 @@
         <v>12</v>
       </c>
       <c r="G3" s="1">
+        <v>41</v>
+      </c>
+      <c r="H3" s="1">
         <v>39563</v>
       </c>
-      <c r="H3" s="1">
+      <c r="I3" s="1">
         <v>43875</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3" s="1">
         <v>244</v>
       </c>
-      <c r="J3" s="1">
+      <c r="K3" s="1">
         <v>98</v>
-      </c>
-      <c r="K3" s="1">
-        <v>146</v>
       </c>
       <c r="L3" s="1">
         <v>146</v>
       </c>
       <c r="M3" s="1">
+        <v>146</v>
+      </c>
+      <c r="N3" s="1">
         <v>98</v>
       </c>
-      <c r="N3" s="1">
+      <c r="O3" s="1">
         <v>1170</v>
-      </c>
-      <c r="O3" s="1">
-        <v>4875</v>
       </c>
       <c r="P3" s="1">
         <v>4875</v>
@@ -775,8 +782,11 @@
       <c r="Q3" s="1">
         <v>4875</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R3" s="1">
+        <v>4875</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>2019</v>
       </c>
@@ -796,31 +806,31 @@
         <v>11</v>
       </c>
       <c r="G4" s="1">
+        <v>44</v>
+      </c>
+      <c r="H4" s="1">
         <v>36612</v>
       </c>
-      <c r="H4" s="1">
+      <c r="I4" s="1">
         <v>40680</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4" s="1">
         <v>226</v>
       </c>
-      <c r="J4" s="1">
+      <c r="K4" s="1">
         <v>90</v>
-      </c>
-      <c r="K4" s="1">
-        <v>136</v>
       </c>
       <c r="L4" s="1">
         <v>136</v>
       </c>
       <c r="M4" s="1">
+        <v>136</v>
+      </c>
+      <c r="N4" s="1">
         <v>90</v>
       </c>
-      <c r="N4" s="1">
+      <c r="O4" s="1">
         <v>1085</v>
-      </c>
-      <c r="O4" s="1">
-        <v>4520</v>
       </c>
       <c r="P4" s="1">
         <v>4520</v>
@@ -828,8 +838,11 @@
       <c r="Q4" s="1">
         <v>4520</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R4" s="1">
+        <v>4520</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>2019</v>
       </c>
@@ -849,31 +862,31 @@
         <v>12</v>
       </c>
       <c r="G5" s="1">
+        <v>48</v>
+      </c>
+      <c r="H5" s="1">
         <v>34125</v>
       </c>
-      <c r="H5" s="1">
+      <c r="I5" s="1">
         <v>37917</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5" s="1">
         <v>211</v>
       </c>
-      <c r="J5" s="1">
+      <c r="K5" s="1">
         <v>84</v>
-      </c>
-      <c r="K5" s="1">
-        <v>126</v>
       </c>
       <c r="L5" s="1">
         <v>126</v>
       </c>
       <c r="M5" s="1">
+        <v>126</v>
+      </c>
+      <c r="N5" s="1">
         <v>84</v>
       </c>
-      <c r="N5" s="1">
+      <c r="O5" s="1">
         <v>1011</v>
-      </c>
-      <c r="O5" s="1">
-        <v>4213</v>
       </c>
       <c r="P5" s="1">
         <v>4213</v>
@@ -881,8 +894,11 @@
       <c r="Q5" s="1">
         <v>4213</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R5" s="1">
+        <v>4213</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>2019</v>
       </c>
@@ -902,31 +918,31 @@
         <v>14</v>
       </c>
       <c r="G6" s="1">
+        <v>36</v>
+      </c>
+      <c r="H6" s="1">
         <v>32254</v>
       </c>
-      <c r="H6" s="1">
+      <c r="I6" s="1">
         <v>35838</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6" s="1">
         <v>199</v>
       </c>
-      <c r="J6" s="1">
+      <c r="K6" s="1">
         <v>80</v>
-      </c>
-      <c r="K6" s="1">
-        <v>119</v>
       </c>
       <c r="L6" s="1">
         <v>119</v>
       </c>
       <c r="M6" s="1">
+        <v>119</v>
+      </c>
+      <c r="N6" s="1">
         <v>80</v>
       </c>
-      <c r="N6" s="1">
+      <c r="O6" s="1">
         <v>956</v>
-      </c>
-      <c r="O6" s="1">
-        <v>3982</v>
       </c>
       <c r="P6" s="1">
         <v>3982</v>
@@ -934,8 +950,11 @@
       <c r="Q6" s="1">
         <v>3982</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R6" s="1">
+        <v>3982</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>2019</v>
       </c>
@@ -955,31 +974,31 @@
         <v>13</v>
       </c>
       <c r="G7" s="1">
+        <v>46</v>
+      </c>
+      <c r="H7" s="1">
         <v>29565</v>
       </c>
-      <c r="H7" s="1">
+      <c r="I7" s="1">
         <v>32850</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7" s="1">
         <v>183</v>
       </c>
-      <c r="J7" s="1">
+      <c r="K7" s="1">
         <v>73</v>
-      </c>
-      <c r="K7" s="1">
-        <v>110</v>
       </c>
       <c r="L7" s="1">
         <v>110</v>
       </c>
       <c r="M7" s="1">
+        <v>110</v>
+      </c>
+      <c r="N7" s="1">
         <v>73</v>
       </c>
-      <c r="N7" s="1">
+      <c r="O7" s="1">
         <v>876</v>
-      </c>
-      <c r="O7" s="1">
-        <v>3650</v>
       </c>
       <c r="P7" s="1">
         <v>3650</v>
@@ -987,8 +1006,11 @@
       <c r="Q7" s="1">
         <v>3650</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R7" s="1">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>2019</v>
       </c>
@@ -1008,31 +1030,31 @@
         <v>13</v>
       </c>
       <c r="G8" s="1">
+        <v>50</v>
+      </c>
+      <c r="H8" s="1">
         <v>26957</v>
       </c>
-      <c r="H8" s="1">
+      <c r="I8" s="1">
         <v>29952</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8" s="1">
         <v>166</v>
       </c>
-      <c r="J8" s="1">
+      <c r="K8" s="1">
         <v>67</v>
-      </c>
-      <c r="K8" s="1">
-        <v>100</v>
       </c>
       <c r="L8" s="1">
         <v>100</v>
       </c>
       <c r="M8" s="1">
+        <v>100</v>
+      </c>
+      <c r="N8" s="1">
         <v>67</v>
       </c>
-      <c r="N8" s="1">
+      <c r="O8" s="1">
         <v>798</v>
-      </c>
-      <c r="O8" s="1">
-        <v>3328</v>
       </c>
       <c r="P8" s="1">
         <v>3328</v>
@@ -1040,8 +1062,11 @@
       <c r="Q8" s="1">
         <v>3328</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R8" s="1">
+        <v>3328</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>2019</v>
       </c>
@@ -1061,31 +1086,31 @@
         <v>14</v>
       </c>
       <c r="G9" s="1">
+        <v>54</v>
+      </c>
+      <c r="H9" s="1">
         <v>25078</v>
       </c>
-      <c r="H9" s="1">
+      <c r="I9" s="1">
         <v>27864</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9" s="1">
         <v>155</v>
       </c>
-      <c r="J9" s="1">
+      <c r="K9" s="1">
         <v>62</v>
-      </c>
-      <c r="K9" s="1">
-        <v>93</v>
       </c>
       <c r="L9" s="1">
         <v>93</v>
       </c>
       <c r="M9" s="1">
+        <v>93</v>
+      </c>
+      <c r="N9" s="1">
         <v>62</v>
       </c>
-      <c r="N9" s="1">
+      <c r="O9" s="1">
         <v>743</v>
-      </c>
-      <c r="O9" s="1">
-        <v>3096</v>
       </c>
       <c r="P9" s="1">
         <v>3096</v>
@@ -1093,8 +1118,11 @@
       <c r="Q9" s="1">
         <v>3096</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R9" s="1">
+        <v>3096</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>2019</v>
       </c>
@@ -1114,31 +1142,31 @@
         <v>15</v>
       </c>
       <c r="G10" s="1">
+        <v>43</v>
+      </c>
+      <c r="H10" s="1">
         <v>23417</v>
       </c>
-      <c r="H10" s="1">
+      <c r="I10" s="1">
         <v>26019</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10" s="1">
         <v>145</v>
       </c>
-      <c r="J10" s="1">
+      <c r="K10" s="1">
         <v>58</v>
-      </c>
-      <c r="K10" s="1">
-        <v>87</v>
       </c>
       <c r="L10" s="1">
         <v>87</v>
       </c>
       <c r="M10" s="1">
+        <v>87</v>
+      </c>
+      <c r="N10" s="1">
         <v>58</v>
       </c>
-      <c r="N10" s="1">
+      <c r="O10" s="1">
         <v>694</v>
-      </c>
-      <c r="O10" s="1">
-        <v>2891</v>
       </c>
       <c r="P10" s="1">
         <v>2891</v>
@@ -1146,8 +1174,11 @@
       <c r="Q10" s="1">
         <v>2891</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R10" s="1">
+        <v>2891</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>2019</v>
       </c>
@@ -1167,31 +1198,31 @@
         <v>16</v>
       </c>
       <c r="G11" s="1">
+        <v>37</v>
+      </c>
+      <c r="H11" s="1">
         <v>21967</v>
       </c>
-      <c r="H11" s="1">
+      <c r="I11" s="1">
         <v>24408</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11" s="1">
         <v>136</v>
       </c>
-      <c r="J11" s="1">
+      <c r="K11" s="1">
         <v>54</v>
-      </c>
-      <c r="K11" s="1">
-        <v>81</v>
       </c>
       <c r="L11" s="1">
         <v>81</v>
       </c>
       <c r="M11" s="1">
+        <v>81</v>
+      </c>
+      <c r="N11" s="1">
         <v>54</v>
       </c>
-      <c r="N11" s="1">
+      <c r="O11" s="1">
         <v>651</v>
-      </c>
-      <c r="O11" s="1">
-        <v>2712</v>
       </c>
       <c r="P11" s="1">
         <v>2712</v>
@@ -1199,8 +1230,11 @@
       <c r="Q11" s="1">
         <v>2712</v>
       </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R11" s="1">
+        <v>2712</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>2019</v>
       </c>
@@ -1220,31 +1254,31 @@
         <v>14</v>
       </c>
       <c r="G12" s="1">
+        <v>47</v>
+      </c>
+      <c r="H12" s="1">
         <v>20444</v>
       </c>
-      <c r="H12" s="1">
+      <c r="I12" s="1">
         <v>22716</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12" s="1">
         <v>126</v>
       </c>
-      <c r="J12" s="1">
+      <c r="K12" s="1">
         <v>50</v>
-      </c>
-      <c r="K12" s="1">
-        <v>76</v>
       </c>
       <c r="L12" s="1">
         <v>76</v>
       </c>
       <c r="M12" s="1">
+        <v>76</v>
+      </c>
+      <c r="N12" s="1">
         <v>50</v>
       </c>
-      <c r="N12" s="1">
+      <c r="O12" s="1">
         <v>606</v>
-      </c>
-      <c r="O12" s="1">
-        <v>2524</v>
       </c>
       <c r="P12" s="1">
         <v>2524</v>
@@ -1252,8 +1286,11 @@
       <c r="Q12" s="1">
         <v>2524</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R12" s="1">
+        <v>2524</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>2019</v>
       </c>
@@ -1273,31 +1310,31 @@
         <v>15</v>
       </c>
       <c r="G13" s="1">
+        <v>40</v>
+      </c>
+      <c r="H13" s="1">
         <v>18881</v>
       </c>
-      <c r="H13" s="1">
+      <c r="I13" s="1">
         <v>20979</v>
       </c>
-      <c r="I13" s="1">
+      <c r="J13" s="1">
         <v>117</v>
       </c>
-      <c r="J13" s="1">
+      <c r="K13" s="1">
         <v>47</v>
-      </c>
-      <c r="K13" s="1">
-        <v>70</v>
       </c>
       <c r="L13" s="1">
         <v>70</v>
       </c>
       <c r="M13" s="1">
+        <v>70</v>
+      </c>
+      <c r="N13" s="1">
         <v>47</v>
       </c>
-      <c r="N13" s="1">
+      <c r="O13" s="1">
         <v>559</v>
-      </c>
-      <c r="O13" s="1">
-        <v>2331</v>
       </c>
       <c r="P13" s="1">
         <v>2331</v>
@@ -1305,8 +1342,11 @@
       <c r="Q13" s="1">
         <v>2331</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R13" s="1">
+        <v>2331</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>2019</v>
       </c>
@@ -1326,31 +1366,31 @@
         <v>17</v>
       </c>
       <c r="G14" s="1">
+        <v>35</v>
+      </c>
+      <c r="H14" s="1">
         <v>17374</v>
       </c>
-      <c r="H14" s="1">
+      <c r="I14" s="1">
         <v>19305</v>
       </c>
-      <c r="I14" s="1">
+      <c r="J14" s="1">
         <v>107</v>
       </c>
-      <c r="J14" s="1">
+      <c r="K14" s="1">
         <v>43</v>
-      </c>
-      <c r="K14" s="1">
-        <v>64</v>
       </c>
       <c r="L14" s="1">
         <v>64</v>
       </c>
       <c r="M14" s="1">
+        <v>64</v>
+      </c>
+      <c r="N14" s="1">
         <v>43</v>
       </c>
-      <c r="N14" s="1">
+      <c r="O14" s="1">
         <v>515</v>
-      </c>
-      <c r="O14" s="1">
-        <v>2145</v>
       </c>
       <c r="P14" s="1">
         <v>2145</v>
@@ -1358,8 +1398,11 @@
       <c r="Q14" s="1">
         <v>2145</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R14" s="1">
+        <v>2145</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>2019</v>
       </c>
@@ -1379,31 +1422,31 @@
         <v>18</v>
       </c>
       <c r="G15" s="1">
+        <v>42</v>
+      </c>
+      <c r="H15" s="1">
         <v>13997</v>
       </c>
-      <c r="H15" s="1">
+      <c r="I15" s="1">
         <v>15552</v>
       </c>
-      <c r="I15" s="1">
+      <c r="J15" s="1">
         <v>86</v>
       </c>
-      <c r="J15" s="1">
+      <c r="K15" s="1">
         <v>35</v>
-      </c>
-      <c r="K15" s="1">
-        <v>52</v>
       </c>
       <c r="L15" s="1">
         <v>52</v>
       </c>
       <c r="M15" s="1">
+        <v>52</v>
+      </c>
+      <c r="N15" s="1">
         <v>35</v>
       </c>
-      <c r="N15" s="1">
+      <c r="O15" s="1">
         <v>415</v>
-      </c>
-      <c r="O15" s="1">
-        <v>1728</v>
       </c>
       <c r="P15" s="1">
         <v>1728</v>
@@ -1411,8 +1454,11 @@
       <c r="Q15" s="1">
         <v>1728</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R15" s="1">
+        <v>1728</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>2021</v>
       </c>
@@ -1432,31 +1478,31 @@
         <v>12</v>
       </c>
       <c r="G16" s="1">
+        <v>49</v>
+      </c>
+      <c r="H16" s="1">
         <v>120867</v>
       </c>
-      <c r="H16" s="1">
+      <c r="I16" s="1">
         <v>134748</v>
       </c>
-      <c r="I16" s="1">
+      <c r="J16" s="1">
         <v>743</v>
       </c>
-      <c r="J16" s="1">
+      <c r="K16" s="1">
         <v>297</v>
-      </c>
-      <c r="K16" s="1">
-        <v>446</v>
       </c>
       <c r="L16" s="1">
         <v>446</v>
       </c>
       <c r="M16" s="1">
+        <v>446</v>
+      </c>
+      <c r="N16" s="1">
         <v>297</v>
       </c>
-      <c r="N16" s="1">
+      <c r="O16" s="1">
         <v>3570</v>
-      </c>
-      <c r="O16" s="1">
-        <v>14872</v>
       </c>
       <c r="P16" s="1">
         <v>14872</v>
@@ -1464,8 +1510,11 @@
       <c r="Q16" s="1">
         <v>14872</v>
       </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R16" s="1">
+        <v>14872</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>2021</v>
       </c>
@@ -1485,31 +1534,31 @@
         <v>11</v>
       </c>
       <c r="G17" s="1">
+        <v>45</v>
+      </c>
+      <c r="H17" s="1">
         <v>112996</v>
       </c>
-      <c r="H17" s="1">
+      <c r="I17" s="1">
         <v>126243</v>
       </c>
-      <c r="I17" s="1">
+      <c r="J17" s="1">
         <v>695</v>
       </c>
-      <c r="J17" s="1">
+      <c r="K17" s="1">
         <v>278</v>
-      </c>
-      <c r="K17" s="1">
-        <v>417</v>
       </c>
       <c r="L17" s="1">
         <v>417</v>
       </c>
       <c r="M17" s="1">
+        <v>417</v>
+      </c>
+      <c r="N17" s="1">
         <v>278</v>
       </c>
-      <c r="N17" s="1">
+      <c r="O17" s="1">
         <v>3340</v>
-      </c>
-      <c r="O17" s="1">
-        <v>13915</v>
       </c>
       <c r="P17" s="1">
         <v>13915</v>
@@ -1517,8 +1566,11 @@
       <c r="Q17" s="1">
         <v>13915</v>
       </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R17" s="1">
+        <v>13915</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
         <v>2021</v>
       </c>
@@ -1538,31 +1590,31 @@
         <v>13</v>
       </c>
       <c r="G18" s="1">
+        <v>38</v>
+      </c>
+      <c r="H18" s="1">
         <v>98244</v>
       </c>
-      <c r="H18" s="1">
+      <c r="I18" s="1">
         <v>109836</v>
       </c>
-      <c r="I18" s="1">
+      <c r="J18" s="1">
         <v>605</v>
       </c>
-      <c r="J18" s="1">
+      <c r="K18" s="1">
         <v>242</v>
-      </c>
-      <c r="K18" s="1">
-        <v>363</v>
       </c>
       <c r="L18" s="1">
         <v>363</v>
       </c>
       <c r="M18" s="1">
+        <v>363</v>
+      </c>
+      <c r="N18" s="1">
         <v>242</v>
       </c>
-      <c r="N18" s="1">
+      <c r="O18" s="1">
         <v>2905</v>
-      </c>
-      <c r="O18" s="1">
-        <v>12104</v>
       </c>
       <c r="P18" s="1">
         <v>12104</v>
@@ -1570,8 +1622,11 @@
       <c r="Q18" s="1">
         <v>12104</v>
       </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R18" s="1">
+        <v>12104</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>2021</v>
       </c>
@@ -1591,31 +1646,31 @@
         <v>12</v>
       </c>
       <c r="G19" s="1">
+        <v>43</v>
+      </c>
+      <c r="H19" s="1">
         <v>104233</v>
       </c>
-      <c r="H19" s="1">
+      <c r="I19" s="1">
         <v>116514</v>
       </c>
-      <c r="I19" s="1">
+      <c r="J19" s="1">
         <v>642</v>
       </c>
-      <c r="J19" s="1">
+      <c r="K19" s="1">
         <v>257</v>
-      </c>
-      <c r="K19" s="1">
-        <v>386</v>
       </c>
       <c r="L19" s="1">
         <v>386</v>
       </c>
       <c r="M19" s="1">
+        <v>386</v>
+      </c>
+      <c r="N19" s="1">
         <v>257</v>
       </c>
-      <c r="N19" s="1">
+      <c r="O19" s="1">
         <v>3086</v>
-      </c>
-      <c r="O19" s="1">
-        <v>12846</v>
       </c>
       <c r="P19" s="1">
         <v>12846</v>
@@ -1623,8 +1678,11 @@
       <c r="Q19" s="1">
         <v>12846</v>
       </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R19" s="1">
+        <v>12846</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
         <v>2021</v>
       </c>
@@ -1644,31 +1702,31 @@
         <v>13</v>
       </c>
       <c r="G20" s="1">
+        <v>51</v>
+      </c>
+      <c r="H20" s="1">
         <v>92351</v>
       </c>
-      <c r="H20" s="1">
+      <c r="I20" s="1">
         <v>103038</v>
       </c>
-      <c r="I20" s="1">
+      <c r="J20" s="1">
         <v>569</v>
       </c>
-      <c r="J20" s="1">
+      <c r="K20" s="1">
         <v>228</v>
-      </c>
-      <c r="K20" s="1">
-        <v>341</v>
       </c>
       <c r="L20" s="1">
         <v>341</v>
       </c>
       <c r="M20" s="1">
+        <v>341</v>
+      </c>
+      <c r="N20" s="1">
         <v>228</v>
       </c>
-      <c r="N20" s="1">
+      <c r="O20" s="1">
         <v>2731</v>
-      </c>
-      <c r="O20" s="1">
-        <v>11382</v>
       </c>
       <c r="P20" s="1">
         <v>11382</v>
@@ -1676,8 +1734,11 @@
       <c r="Q20" s="1">
         <v>11382</v>
       </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R20" s="1">
+        <v>11382</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
         <v>2021</v>
       </c>
@@ -1697,31 +1758,31 @@
         <v>14</v>
       </c>
       <c r="G21" s="1">
+        <v>47</v>
+      </c>
+      <c r="H21" s="1">
         <v>79545</v>
       </c>
-      <c r="H21" s="1">
+      <c r="I21" s="1">
         <v>88578</v>
       </c>
-      <c r="I21" s="1">
+      <c r="J21" s="1">
         <v>490</v>
       </c>
-      <c r="J21" s="1">
+      <c r="K21" s="1">
         <v>196</v>
-      </c>
-      <c r="K21" s="1">
-        <v>294</v>
       </c>
       <c r="L21" s="1">
         <v>294</v>
       </c>
       <c r="M21" s="1">
+        <v>294</v>
+      </c>
+      <c r="N21" s="1">
         <v>196</v>
       </c>
-      <c r="N21" s="1">
+      <c r="O21" s="1">
         <v>2353</v>
-      </c>
-      <c r="O21" s="1">
-        <v>9804</v>
       </c>
       <c r="P21" s="1">
         <v>9804</v>
@@ -1729,8 +1790,11 @@
       <c r="Q21" s="1">
         <v>9804</v>
       </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R21" s="1">
+        <v>9804</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
         <v>2021</v>
       </c>
@@ -1750,31 +1814,31 @@
         <v>13</v>
       </c>
       <c r="G22" s="1">
+        <v>55</v>
+      </c>
+      <c r="H22" s="1">
         <v>83286</v>
       </c>
-      <c r="H22" s="1">
+      <c r="I22" s="1">
         <v>92652</v>
       </c>
-      <c r="I22" s="1">
+      <c r="J22" s="1">
         <v>512</v>
       </c>
-      <c r="J22" s="1">
+      <c r="K22" s="1">
         <v>205</v>
-      </c>
-      <c r="K22" s="1">
-        <v>307</v>
       </c>
       <c r="L22" s="1">
         <v>307</v>
       </c>
       <c r="M22" s="1">
+        <v>307</v>
+      </c>
+      <c r="N22" s="1">
         <v>205</v>
       </c>
-      <c r="N22" s="1">
+      <c r="O22" s="1">
         <v>2463</v>
-      </c>
-      <c r="O22" s="1">
-        <v>10265</v>
       </c>
       <c r="P22" s="1">
         <v>10265</v>
@@ -1782,8 +1846,11 @@
       <c r="Q22" s="1">
         <v>10265</v>
       </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R22" s="1">
+        <v>10265</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>2021</v>
       </c>
@@ -1803,31 +1870,31 @@
         <v>15</v>
       </c>
       <c r="G23" s="1">
+        <v>44</v>
+      </c>
+      <c r="H23" s="1">
         <v>73129</v>
       </c>
-      <c r="H23" s="1">
+      <c r="I23" s="1">
         <v>81432</v>
       </c>
-      <c r="I23" s="1">
+      <c r="J23" s="1">
         <v>450</v>
       </c>
-      <c r="J23" s="1">
+      <c r="K23" s="1">
         <v>180</v>
-      </c>
-      <c r="K23" s="1">
-        <v>270</v>
       </c>
       <c r="L23" s="1">
         <v>270</v>
       </c>
       <c r="M23" s="1">
+        <v>270</v>
+      </c>
+      <c r="N23" s="1">
         <v>180</v>
       </c>
-      <c r="N23" s="1">
+      <c r="O23" s="1">
         <v>2163</v>
-      </c>
-      <c r="O23" s="1">
-        <v>9011</v>
       </c>
       <c r="P23" s="1">
         <v>9011</v>
@@ -1835,8 +1902,11 @@
       <c r="Q23" s="1">
         <v>9011</v>
       </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R23" s="1">
+        <v>9011</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>2021</v>
       </c>
@@ -1856,31 +1926,31 @@
         <v>16</v>
       </c>
       <c r="G24" s="1">
+        <v>36</v>
+      </c>
+      <c r="H24" s="1">
         <v>64088</v>
       </c>
-      <c r="H24" s="1">
+      <c r="I24" s="1">
         <v>71307</v>
       </c>
-      <c r="I24" s="1">
+      <c r="J24" s="1">
         <v>394</v>
       </c>
-      <c r="J24" s="1">
+      <c r="K24" s="1">
         <v>158</v>
-      </c>
-      <c r="K24" s="1">
-        <v>237</v>
       </c>
       <c r="L24" s="1">
         <v>237</v>
       </c>
       <c r="M24" s="1">
+        <v>237</v>
+      </c>
+      <c r="N24" s="1">
         <v>158</v>
       </c>
-      <c r="N24" s="1">
+      <c r="O24" s="1">
         <v>1894</v>
-      </c>
-      <c r="O24" s="1">
-        <v>7895</v>
       </c>
       <c r="P24" s="1">
         <v>7895</v>
@@ -1888,8 +1958,11 @@
       <c r="Q24" s="1">
         <v>7895</v>
       </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R24" s="1">
+        <v>7895</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>2021</v>
       </c>
@@ -1909,31 +1982,31 @@
         <v>14</v>
       </c>
       <c r="G25" s="1">
+        <v>41</v>
+      </c>
+      <c r="H25" s="1">
         <v>68361</v>
       </c>
-      <c r="H25" s="1">
+      <c r="I25" s="1">
         <v>76188</v>
       </c>
-      <c r="I25" s="1">
+      <c r="J25" s="1">
         <v>420</v>
       </c>
-      <c r="J25" s="1">
+      <c r="K25" s="1">
         <v>168</v>
-      </c>
-      <c r="K25" s="1">
-        <v>252</v>
       </c>
       <c r="L25" s="1">
         <v>252</v>
       </c>
       <c r="M25" s="1">
+        <v>252</v>
+      </c>
+      <c r="N25" s="1">
         <v>168</v>
       </c>
-      <c r="N25" s="1">
+      <c r="O25" s="1">
         <v>2019</v>
-      </c>
-      <c r="O25" s="1">
-        <v>8420</v>
       </c>
       <c r="P25" s="1">
         <v>8420</v>
@@ -1941,8 +2014,11 @@
       <c r="Q25" s="1">
         <v>8420</v>
       </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R25" s="1">
+        <v>8420</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" s="6">
         <v>2021</v>
       </c>
@@ -1962,31 +2038,31 @@
         <v>15</v>
       </c>
       <c r="G26" s="1">
+        <v>43</v>
+      </c>
+      <c r="H26" s="1">
         <v>62123</v>
       </c>
-      <c r="H26" s="1">
+      <c r="I26" s="1">
         <v>69210</v>
       </c>
-      <c r="I26" s="1">
+      <c r="J26" s="1">
         <v>382</v>
       </c>
-      <c r="J26" s="1">
+      <c r="K26" s="1">
         <v>153</v>
-      </c>
-      <c r="K26" s="1">
-        <v>229</v>
       </c>
       <c r="L26" s="1">
         <v>229</v>
       </c>
       <c r="M26" s="1">
+        <v>229</v>
+      </c>
+      <c r="N26" s="1">
         <v>153</v>
       </c>
-      <c r="N26" s="1">
+      <c r="O26" s="1">
         <v>1836</v>
-      </c>
-      <c r="O26" s="1">
-        <v>7652</v>
       </c>
       <c r="P26" s="1">
         <v>7652</v>
@@ -1994,8 +2070,11 @@
       <c r="Q26" s="1">
         <v>7652</v>
       </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R26" s="1">
+        <v>7652</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" s="6">
         <v>2021</v>
       </c>
@@ -2015,31 +2094,31 @@
         <v>17</v>
       </c>
       <c r="G27" s="1">
+        <v>39</v>
+      </c>
+      <c r="H27" s="1">
         <v>52669</v>
       </c>
-      <c r="H27" s="1">
+      <c r="I27" s="1">
         <v>58647</v>
       </c>
-      <c r="I27" s="1">
+      <c r="J27" s="1">
         <v>324</v>
       </c>
-      <c r="J27" s="1">
+      <c r="K27" s="1">
         <v>130</v>
-      </c>
-      <c r="K27" s="1">
-        <v>195</v>
       </c>
       <c r="L27" s="1">
         <v>195</v>
       </c>
       <c r="M27" s="1">
+        <v>195</v>
+      </c>
+      <c r="N27" s="1">
         <v>130</v>
       </c>
-      <c r="N27" s="1">
+      <c r="O27" s="1">
         <v>1556</v>
-      </c>
-      <c r="O27" s="1">
-        <v>6483</v>
       </c>
       <c r="P27" s="1">
         <v>6483</v>
@@ -2047,8 +2126,11 @@
       <c r="Q27" s="1">
         <v>6483</v>
       </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R27" s="1">
+        <v>6483</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
         <v>2021</v>
       </c>
@@ -2068,31 +2150,31 @@
         <v>18</v>
       </c>
       <c r="G28" s="1">
+        <v>37</v>
+      </c>
+      <c r="H28" s="1">
         <v>46910</v>
       </c>
-      <c r="H28" s="1">
+      <c r="I28" s="1">
         <v>52341</v>
       </c>
-      <c r="I28" s="1">
+      <c r="J28" s="1">
         <v>289</v>
       </c>
-      <c r="J28" s="1">
+      <c r="K28" s="1">
         <v>116</v>
-      </c>
-      <c r="K28" s="1">
-        <v>174</v>
       </c>
       <c r="L28" s="1">
         <v>174</v>
       </c>
       <c r="M28" s="1">
+        <v>174</v>
+      </c>
+      <c r="N28" s="1">
         <v>116</v>
       </c>
-      <c r="N28" s="1">
+      <c r="O28" s="1">
         <v>1389</v>
-      </c>
-      <c r="O28" s="1">
-        <v>5774</v>
       </c>
       <c r="P28" s="1">
         <v>5774</v>
@@ -2100,8 +2182,11 @@
       <c r="Q28" s="1">
         <v>5774</v>
       </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R28" s="1">
+        <v>5774</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" s="6">
         <v>2024</v>
       </c>
@@ -2121,31 +2206,31 @@
         <v>13</v>
       </c>
       <c r="G29" s="1">
+        <v>47</v>
+      </c>
+      <c r="H29" s="1">
         <v>60435</v>
       </c>
-      <c r="H29" s="1">
+      <c r="I29" s="1">
         <v>67260</v>
       </c>
-      <c r="I29" s="1">
+      <c r="J29" s="1">
         <v>371</v>
       </c>
-      <c r="J29" s="1">
+      <c r="K29" s="1">
         <v>149</v>
-      </c>
-      <c r="K29" s="1">
-        <v>223</v>
       </c>
       <c r="L29" s="1">
         <v>223</v>
       </c>
       <c r="M29" s="1">
+        <v>223</v>
+      </c>
+      <c r="N29" s="1">
         <v>149</v>
       </c>
-      <c r="N29" s="1">
+      <c r="O29" s="1">
         <v>1786</v>
-      </c>
-      <c r="O29" s="1">
-        <v>7450</v>
       </c>
       <c r="P29" s="1">
         <v>7450</v>
@@ -2153,8 +2238,11 @@
       <c r="Q29" s="1">
         <v>7450</v>
       </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R29" s="1">
+        <v>7450</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" s="6">
         <v>2024</v>
       </c>
@@ -2174,31 +2262,31 @@
         <v>12</v>
       </c>
       <c r="G30" s="1">
+        <v>50</v>
+      </c>
+      <c r="H30" s="1">
         <v>56941</v>
       </c>
-      <c r="H30" s="1">
+      <c r="I30" s="1">
         <v>63306</v>
       </c>
-      <c r="I30" s="1">
+      <c r="J30" s="1">
         <v>349</v>
       </c>
-      <c r="J30" s="1">
+      <c r="K30" s="1">
         <v>140</v>
-      </c>
-      <c r="K30" s="1">
-        <v>210</v>
       </c>
       <c r="L30" s="1">
         <v>210</v>
       </c>
       <c r="M30" s="1">
+        <v>210</v>
+      </c>
+      <c r="N30" s="1">
         <v>140</v>
       </c>
-      <c r="N30" s="1">
+      <c r="O30" s="1">
         <v>1684</v>
-      </c>
-      <c r="O30" s="1">
-        <v>7021</v>
       </c>
       <c r="P30" s="1">
         <v>7021</v>
@@ -2206,8 +2294,11 @@
       <c r="Q30" s="1">
         <v>7021</v>
       </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R30" s="1">
+        <v>7021</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" s="6">
         <v>2024</v>
       </c>
@@ -2227,31 +2318,31 @@
         <v>12</v>
       </c>
       <c r="G31" s="1">
+        <v>44</v>
+      </c>
+      <c r="H31" s="1">
         <v>54656</v>
       </c>
-      <c r="H31" s="1">
+      <c r="I31" s="1">
         <v>60750</v>
       </c>
-      <c r="I31" s="1">
+      <c r="J31" s="1">
         <v>335</v>
       </c>
-      <c r="J31" s="1">
+      <c r="K31" s="1">
         <v>134</v>
-      </c>
-      <c r="K31" s="1">
-        <v>201</v>
       </c>
       <c r="L31" s="1">
         <v>201</v>
       </c>
       <c r="M31" s="1">
+        <v>201</v>
+      </c>
+      <c r="N31" s="1">
         <v>134</v>
       </c>
-      <c r="N31" s="1">
+      <c r="O31" s="1">
         <v>1612</v>
-      </c>
-      <c r="O31" s="1">
-        <v>6738</v>
       </c>
       <c r="P31" s="1">
         <v>6738</v>
@@ -2259,8 +2350,11 @@
       <c r="Q31" s="1">
         <v>6738</v>
       </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R31" s="1">
+        <v>6738</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" s="6">
         <v>2024</v>
       </c>
@@ -2280,31 +2374,31 @@
         <v>13</v>
       </c>
       <c r="G32" s="1">
+        <v>42</v>
+      </c>
+      <c r="H32" s="1">
         <v>49873</v>
       </c>
-      <c r="H32" s="1">
+      <c r="I32" s="1">
         <v>55428</v>
       </c>
-      <c r="I32" s="1">
+      <c r="J32" s="1">
         <v>306</v>
       </c>
-      <c r="J32" s="1">
+      <c r="K32" s="1">
         <v>122</v>
-      </c>
-      <c r="K32" s="1">
-        <v>184</v>
       </c>
       <c r="L32" s="1">
         <v>184</v>
       </c>
       <c r="M32" s="1">
+        <v>184</v>
+      </c>
+      <c r="N32" s="1">
         <v>122</v>
       </c>
-      <c r="N32" s="1">
+      <c r="O32" s="1">
         <v>1477</v>
-      </c>
-      <c r="O32" s="1">
-        <v>6154</v>
       </c>
       <c r="P32" s="1">
         <v>6154</v>
@@ -2312,8 +2406,11 @@
       <c r="Q32" s="1">
         <v>6154</v>
       </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R32" s="1">
+        <v>6154</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" s="6">
         <v>2024</v>
       </c>
@@ -2333,31 +2430,31 @@
         <v>12</v>
       </c>
       <c r="G33" s="1">
+        <v>54</v>
+      </c>
+      <c r="H33" s="1">
         <v>44061</v>
       </c>
-      <c r="H33" s="1">
+      <c r="I33" s="1">
         <v>48960</v>
       </c>
-      <c r="I33" s="1">
+      <c r="J33" s="1">
         <v>270</v>
       </c>
-      <c r="J33" s="1">
+      <c r="K33" s="1">
         <v>108</v>
-      </c>
-      <c r="K33" s="1">
-        <v>163</v>
       </c>
       <c r="L33" s="1">
         <v>163</v>
       </c>
       <c r="M33" s="1">
+        <v>163</v>
+      </c>
+      <c r="N33" s="1">
         <v>108</v>
       </c>
-      <c r="N33" s="1">
+      <c r="O33" s="1">
         <v>1303</v>
-      </c>
-      <c r="O33" s="1">
-        <v>5432</v>
       </c>
       <c r="P33" s="1">
         <v>5432</v>
@@ -2365,8 +2462,11 @@
       <c r="Q33" s="1">
         <v>5432</v>
       </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R33" s="1">
+        <v>5432</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" s="6">
         <v>2024</v>
       </c>
@@ -2386,31 +2486,31 @@
         <v>13</v>
       </c>
       <c r="G34" s="1">
+        <v>39</v>
+      </c>
+      <c r="H34" s="1">
         <v>52931</v>
       </c>
-      <c r="H34" s="1">
+      <c r="I34" s="1">
         <v>59004</v>
       </c>
-      <c r="I34" s="1">
+      <c r="J34" s="1">
         <v>325</v>
       </c>
-      <c r="J34" s="1">
+      <c r="K34" s="1">
         <v>130</v>
-      </c>
-      <c r="K34" s="1">
-        <v>195</v>
       </c>
       <c r="L34" s="1">
         <v>195</v>
       </c>
       <c r="M34" s="1">
+        <v>195</v>
+      </c>
+      <c r="N34" s="1">
         <v>130</v>
       </c>
-      <c r="N34" s="1">
+      <c r="O34" s="1">
         <v>1565</v>
-      </c>
-      <c r="O34" s="1">
-        <v>6522</v>
       </c>
       <c r="P34" s="1">
         <v>6522</v>
@@ -2418,8 +2518,11 @@
       <c r="Q34" s="1">
         <v>6522</v>
       </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R34" s="1">
+        <v>6522</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" s="6">
         <v>2024</v>
       </c>
@@ -2439,31 +2542,31 @@
         <v>13</v>
       </c>
       <c r="G35" s="1">
+        <v>48</v>
+      </c>
+      <c r="H35" s="1">
         <v>46904</v>
       </c>
-      <c r="H35" s="1">
+      <c r="I35" s="1">
         <v>52200</v>
       </c>
-      <c r="I35" s="1">
+      <c r="J35" s="1">
         <v>288</v>
       </c>
-      <c r="J35" s="1">
+      <c r="K35" s="1">
         <v>115</v>
-      </c>
-      <c r="K35" s="1">
-        <v>173</v>
       </c>
       <c r="L35" s="1">
         <v>173</v>
       </c>
       <c r="M35" s="1">
+        <v>173</v>
+      </c>
+      <c r="N35" s="1">
         <v>115</v>
       </c>
-      <c r="N35" s="1">
+      <c r="O35" s="1">
         <v>1387</v>
-      </c>
-      <c r="O35" s="1">
-        <v>5780</v>
       </c>
       <c r="P35" s="1">
         <v>5780</v>
@@ -2471,8 +2574,11 @@
       <c r="Q35" s="1">
         <v>5780</v>
       </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R35" s="1">
+        <v>5780</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" s="6">
         <v>2024</v>
       </c>
@@ -2492,31 +2598,31 @@
         <v>15</v>
       </c>
       <c r="G36" s="1">
+        <v>43</v>
+      </c>
+      <c r="H36" s="1">
         <v>40461</v>
       </c>
-      <c r="H36" s="1">
+      <c r="I36" s="1">
         <v>45054</v>
       </c>
-      <c r="I36" s="1">
+      <c r="J36" s="1">
         <v>249</v>
       </c>
-      <c r="J36" s="1">
+      <c r="K36" s="1">
         <v>100</v>
-      </c>
-      <c r="K36" s="1">
-        <v>149</v>
       </c>
       <c r="L36" s="1">
         <v>149</v>
       </c>
       <c r="M36" s="1">
+        <v>149</v>
+      </c>
+      <c r="N36" s="1">
         <v>100</v>
       </c>
-      <c r="N36" s="1">
+      <c r="O36" s="1">
         <v>1197</v>
-      </c>
-      <c r="O36" s="1">
-        <v>4988</v>
       </c>
       <c r="P36" s="1">
         <v>4988</v>
@@ -2524,8 +2630,11 @@
       <c r="Q36" s="1">
         <v>4988</v>
       </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R36" s="1">
+        <v>4988</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" s="6">
         <v>2024</v>
       </c>
@@ -2545,31 +2654,31 @@
         <v>14</v>
       </c>
       <c r="G37" s="1">
+        <v>46</v>
+      </c>
+      <c r="H37" s="1">
         <v>37038</v>
       </c>
-      <c r="H37" s="1">
+      <c r="I37" s="1">
         <v>41364</v>
       </c>
-      <c r="I37" s="1">
+      <c r="J37" s="1">
         <v>228</v>
       </c>
-      <c r="J37" s="1">
+      <c r="K37" s="1">
         <v>91</v>
-      </c>
-      <c r="K37" s="1">
-        <v>137</v>
       </c>
       <c r="L37" s="1">
         <v>137</v>
       </c>
       <c r="M37" s="1">
+        <v>137</v>
+      </c>
+      <c r="N37" s="1">
         <v>91</v>
       </c>
-      <c r="N37" s="1">
+      <c r="O37" s="1">
         <v>1096</v>
-      </c>
-      <c r="O37" s="1">
-        <v>4567</v>
       </c>
       <c r="P37" s="1">
         <v>4567</v>
@@ -2577,8 +2686,11 @@
       <c r="Q37" s="1">
         <v>4567</v>
       </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R37" s="1">
+        <v>4567</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" s="6">
         <v>2024</v>
       </c>
@@ -2598,31 +2710,31 @@
         <v>16</v>
       </c>
       <c r="G38" s="1">
+        <v>44</v>
+      </c>
+      <c r="H38" s="1">
         <v>34301</v>
       </c>
-      <c r="H38" s="1">
+      <c r="I38" s="1">
         <v>38250</v>
       </c>
-      <c r="I38" s="1">
+      <c r="J38" s="1">
         <v>211</v>
       </c>
-      <c r="J38" s="1">
+      <c r="K38" s="1">
         <v>84</v>
-      </c>
-      <c r="K38" s="1">
-        <v>127</v>
       </c>
       <c r="L38" s="1">
         <v>127</v>
       </c>
       <c r="M38" s="1">
+        <v>127</v>
+      </c>
+      <c r="N38" s="1">
         <v>84</v>
       </c>
-      <c r="N38" s="1">
+      <c r="O38" s="1">
         <v>1015</v>
-      </c>
-      <c r="O38" s="1">
-        <v>4230</v>
       </c>
       <c r="P38" s="1">
         <v>4230</v>
@@ -2630,8 +2742,11 @@
       <c r="Q38" s="1">
         <v>4230</v>
       </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R38" s="1">
+        <v>4230</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" s="6">
         <v>2024</v>
       </c>
@@ -2651,31 +2766,31 @@
         <v>15</v>
       </c>
       <c r="G39" s="1">
+        <v>41</v>
+      </c>
+      <c r="H39" s="1">
         <v>31801</v>
       </c>
-      <c r="H39" s="1">
+      <c r="I39" s="1">
         <v>35514</v>
       </c>
-      <c r="I39" s="1">
+      <c r="J39" s="1">
         <v>196</v>
       </c>
-      <c r="J39" s="1">
+      <c r="K39" s="1">
         <v>78</v>
-      </c>
-      <c r="K39" s="1">
-        <v>117</v>
       </c>
       <c r="L39" s="1">
         <v>117</v>
       </c>
       <c r="M39" s="1">
+        <v>117</v>
+      </c>
+      <c r="N39" s="1">
         <v>78</v>
       </c>
-      <c r="N39" s="1">
+      <c r="O39" s="1">
         <v>941</v>
-      </c>
-      <c r="O39" s="1">
-        <v>3921</v>
       </c>
       <c r="P39" s="1">
         <v>3921</v>
@@ -2683,8 +2798,11 @@
       <c r="Q39" s="1">
         <v>3921</v>
       </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R39" s="1">
+        <v>3921</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" s="6">
         <v>2024</v>
       </c>
@@ -2704,31 +2822,31 @@
         <v>17</v>
       </c>
       <c r="G40" s="1">
+        <v>45</v>
+      </c>
+      <c r="H40" s="1">
         <v>27972</v>
       </c>
-      <c r="H40" s="1">
+      <c r="I40" s="1">
         <v>31152</v>
       </c>
-      <c r="I40" s="1">
+      <c r="J40" s="1">
         <v>172</v>
       </c>
-      <c r="J40" s="1">
+      <c r="K40" s="1">
         <v>69</v>
-      </c>
-      <c r="K40" s="1">
-        <v>103</v>
       </c>
       <c r="L40" s="1">
         <v>103</v>
       </c>
       <c r="M40" s="1">
+        <v>103</v>
+      </c>
+      <c r="N40" s="1">
         <v>69</v>
       </c>
-      <c r="N40" s="1">
+      <c r="O40" s="1">
         <v>827</v>
-      </c>
-      <c r="O40" s="1">
-        <v>3448</v>
       </c>
       <c r="P40" s="1">
         <v>3448</v>
@@ -2736,8 +2854,11 @@
       <c r="Q40" s="1">
         <v>3448</v>
       </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R40" s="1">
+        <v>3448</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" s="6">
         <v>2024</v>
       </c>
@@ -2757,31 +2878,31 @@
         <v>18</v>
       </c>
       <c r="G41" s="1">
+        <v>38</v>
+      </c>
+      <c r="H41" s="1">
         <v>19644</v>
       </c>
-      <c r="H41" s="1">
+      <c r="I41" s="1">
         <v>21897</v>
       </c>
-      <c r="I41" s="1">
+      <c r="J41" s="1">
         <v>121</v>
       </c>
-      <c r="J41" s="1">
+      <c r="K41" s="1">
         <v>48</v>
-      </c>
-      <c r="K41" s="1">
-        <v>73</v>
       </c>
       <c r="L41" s="1">
         <v>73</v>
       </c>
       <c r="M41" s="1">
+        <v>73</v>
+      </c>
+      <c r="N41" s="1">
         <v>48</v>
       </c>
-      <c r="N41" s="1">
+      <c r="O41" s="1">
         <v>583</v>
-      </c>
-      <c r="O41" s="1">
-        <v>2421</v>
       </c>
       <c r="P41" s="1">
         <v>2421</v>
@@ -2789,8 +2910,11 @@
       <c r="Q41" s="1">
         <v>2421</v>
       </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R41" s="1">
+        <v>2421</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" s="6">
         <v>2025</v>
       </c>
@@ -2810,31 +2934,31 @@
         <v>13</v>
       </c>
       <c r="G42" s="1">
+        <v>35</v>
+      </c>
+      <c r="H42" s="1">
         <v>341851</v>
       </c>
-      <c r="H42" s="1">
+      <c r="I42" s="1">
         <v>380169</v>
       </c>
-      <c r="I42" s="1">
+      <c r="J42" s="1">
         <v>2105</v>
       </c>
-      <c r="J42" s="1">
+      <c r="K42" s="1">
         <v>842</v>
-      </c>
-      <c r="K42" s="1">
-        <v>1263</v>
       </c>
       <c r="L42" s="1">
         <v>1263</v>
       </c>
       <c r="M42" s="1">
+        <v>1263</v>
+      </c>
+      <c r="N42" s="1">
         <v>842</v>
       </c>
-      <c r="N42" s="1">
+      <c r="O42" s="1">
         <v>10105</v>
-      </c>
-      <c r="O42" s="1">
-        <v>42105</v>
       </c>
       <c r="P42" s="1">
         <v>42105</v>
@@ -2842,8 +2966,11 @@
       <c r="Q42" s="1">
         <v>42105</v>
       </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R42" s="1">
+        <v>42105</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43" s="6">
         <v>2025</v>
       </c>
@@ -2863,31 +2990,31 @@
         <v>12</v>
       </c>
       <c r="G43" s="1">
+        <v>42</v>
+      </c>
+      <c r="H43" s="1">
         <v>323724</v>
       </c>
-      <c r="H43" s="1">
+      <c r="I43" s="1">
         <v>360036</v>
       </c>
-      <c r="I43" s="1">
+      <c r="J43" s="1">
         <v>1993</v>
       </c>
-      <c r="J43" s="1">
+      <c r="K43" s="1">
         <v>797</v>
-      </c>
-      <c r="K43" s="1">
-        <v>1196</v>
       </c>
       <c r="L43" s="1">
         <v>1196</v>
       </c>
       <c r="M43" s="1">
+        <v>1196</v>
+      </c>
+      <c r="N43" s="1">
         <v>797</v>
       </c>
-      <c r="N43" s="1">
+      <c r="O43" s="1">
         <v>9570</v>
-      </c>
-      <c r="O43" s="1">
-        <v>39874</v>
       </c>
       <c r="P43" s="1">
         <v>39874</v>
@@ -2895,8 +3022,11 @@
       <c r="Q43" s="1">
         <v>39874</v>
       </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R43" s="1">
+        <v>39874</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44" s="6">
         <v>2025</v>
       </c>
@@ -2916,31 +3046,31 @@
         <v>12</v>
       </c>
       <c r="G44" s="1">
+        <v>47</v>
+      </c>
+      <c r="H44" s="1">
         <v>313379</v>
       </c>
-      <c r="H44" s="1">
+      <c r="I44" s="1">
         <v>348582</v>
       </c>
-      <c r="I44" s="1">
+      <c r="J44" s="1">
         <v>1930</v>
       </c>
-      <c r="J44" s="1">
+      <c r="K44" s="1">
         <v>772</v>
-      </c>
-      <c r="K44" s="1">
-        <v>1158</v>
       </c>
       <c r="L44" s="1">
         <v>1158</v>
       </c>
       <c r="M44" s="1">
+        <v>1158</v>
+      </c>
+      <c r="N44" s="1">
         <v>772</v>
       </c>
-      <c r="N44" s="1">
+      <c r="O44" s="1">
         <v>9259</v>
-      </c>
-      <c r="O44" s="1">
-        <v>38596</v>
       </c>
       <c r="P44" s="1">
         <v>38596</v>
@@ -2948,8 +3078,11 @@
       <c r="Q44" s="1">
         <v>38596</v>
       </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R44" s="1">
+        <v>38596</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45" s="6">
         <v>2025</v>
       </c>
@@ -2969,31 +3102,31 @@
         <v>14</v>
       </c>
       <c r="G45" s="1">
+        <v>44</v>
+      </c>
+      <c r="H45" s="1">
         <v>301316</v>
       </c>
-      <c r="H45" s="1">
+      <c r="I45" s="1">
         <v>336084</v>
       </c>
-      <c r="I45" s="1">
+      <c r="J45" s="1">
         <v>1855</v>
       </c>
-      <c r="J45" s="1">
+      <c r="K45" s="1">
         <v>742</v>
-      </c>
-      <c r="K45" s="1">
-        <v>1113</v>
       </c>
       <c r="L45" s="1">
         <v>1113</v>
       </c>
       <c r="M45" s="1">
+        <v>1113</v>
+      </c>
+      <c r="N45" s="1">
         <v>742</v>
       </c>
-      <c r="N45" s="1">
+      <c r="O45" s="1">
         <v>8946</v>
-      </c>
-      <c r="O45" s="1">
-        <v>37110</v>
       </c>
       <c r="P45" s="1">
         <v>37110</v>
@@ -3001,8 +3134,11 @@
       <c r="Q45" s="1">
         <v>37110</v>
       </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R45" s="1">
+        <v>37110</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A46" s="6">
         <v>2025</v>
       </c>
@@ -3022,31 +3158,31 @@
         <v>13</v>
       </c>
       <c r="G46" s="1">
+        <v>49</v>
+      </c>
+      <c r="H46" s="1">
         <v>290733</v>
       </c>
-      <c r="H46" s="1">
+      <c r="I46" s="1">
         <v>324378</v>
       </c>
-      <c r="I46" s="1">
+      <c r="J46" s="1">
         <v>1792</v>
       </c>
-      <c r="J46" s="1">
+      <c r="K46" s="1">
         <v>717</v>
-      </c>
-      <c r="K46" s="1">
-        <v>1077</v>
       </c>
       <c r="L46" s="1">
         <v>1077</v>
       </c>
       <c r="M46" s="1">
+        <v>1077</v>
+      </c>
+      <c r="N46" s="1">
         <v>717</v>
       </c>
-      <c r="N46" s="1">
+      <c r="O46" s="1">
         <v>8620</v>
-      </c>
-      <c r="O46" s="1">
-        <v>35842</v>
       </c>
       <c r="P46" s="1">
         <v>35842</v>
@@ -3054,8 +3190,11 @@
       <c r="Q46" s="1">
         <v>35842</v>
       </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R46" s="1">
+        <v>35842</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A47" s="6">
         <v>2025</v>
       </c>
@@ -3075,31 +3214,31 @@
         <v>13</v>
       </c>
       <c r="G47" s="1">
+        <v>52</v>
+      </c>
+      <c r="H47" s="1">
         <v>260432</v>
       </c>
-      <c r="H47" s="1">
+      <c r="I47" s="1">
         <v>290817</v>
       </c>
-      <c r="I47" s="1">
+      <c r="J47" s="1">
         <v>1605</v>
       </c>
-      <c r="J47" s="1">
+      <c r="K47" s="1">
         <v>642</v>
-      </c>
-      <c r="K47" s="1">
-        <v>963</v>
       </c>
       <c r="L47" s="1">
         <v>963</v>
       </c>
       <c r="M47" s="1">
+        <v>963</v>
+      </c>
+      <c r="N47" s="1">
         <v>642</v>
       </c>
-      <c r="N47" s="1">
+      <c r="O47" s="1">
         <v>7718</v>
-      </c>
-      <c r="O47" s="1">
-        <v>32105</v>
       </c>
       <c r="P47" s="1">
         <v>32105</v>
@@ -3107,8 +3246,11 @@
       <c r="Q47" s="1">
         <v>32105</v>
       </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R47" s="1">
+        <v>32105</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A48" s="6">
         <v>2025</v>
       </c>
@@ -3128,31 +3270,31 @@
         <v>12</v>
       </c>
       <c r="G48" s="1">
+        <v>48</v>
+      </c>
+      <c r="H48" s="1">
         <v>248009</v>
       </c>
-      <c r="H48" s="1">
+      <c r="I48" s="1">
         <v>276516</v>
       </c>
-      <c r="I48" s="1">
+      <c r="J48" s="1">
         <v>1529</v>
       </c>
-      <c r="J48" s="1">
+      <c r="K48" s="1">
         <v>612</v>
-      </c>
-      <c r="K48" s="1">
-        <v>918</v>
       </c>
       <c r="L48" s="1">
         <v>918</v>
       </c>
       <c r="M48" s="1">
+        <v>918</v>
+      </c>
+      <c r="N48" s="1">
         <v>612</v>
       </c>
-      <c r="N48" s="1">
+      <c r="O48" s="1">
         <v>7357</v>
-      </c>
-      <c r="O48" s="1">
-        <v>30574</v>
       </c>
       <c r="P48" s="1">
         <v>30574</v>
@@ -3160,8 +3302,11 @@
       <c r="Q48" s="1">
         <v>30574</v>
       </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R48" s="1">
+        <v>30574</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49" s="6">
         <v>2025</v>
       </c>
@@ -3181,31 +3326,31 @@
         <v>15</v>
       </c>
       <c r="G49" s="1">
+        <v>37</v>
+      </c>
+      <c r="H49" s="1">
         <v>230612</v>
       </c>
-      <c r="H49" s="1">
+      <c r="I49" s="1">
         <v>256896</v>
       </c>
-      <c r="I49" s="1">
+      <c r="J49" s="1">
         <v>1422</v>
       </c>
-      <c r="J49" s="1">
+      <c r="K49" s="1">
         <v>569</v>
-      </c>
-      <c r="K49" s="1">
-        <v>853</v>
       </c>
       <c r="L49" s="1">
         <v>853</v>
       </c>
       <c r="M49" s="1">
+        <v>853</v>
+      </c>
+      <c r="N49" s="1">
         <v>569</v>
       </c>
-      <c r="N49" s="1">
+      <c r="O49" s="1">
         <v>6844</v>
-      </c>
-      <c r="O49" s="1">
-        <v>28432</v>
       </c>
       <c r="P49" s="1">
         <v>28432</v>
@@ -3213,8 +3358,11 @@
       <c r="Q49" s="1">
         <v>28432</v>
       </c>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R49" s="1">
+        <v>28432</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A50" s="6">
         <v>2025</v>
       </c>
@@ -3234,31 +3382,31 @@
         <v>14</v>
       </c>
       <c r="G50" s="1">
+        <v>43</v>
+      </c>
+      <c r="H50" s="1">
         <v>214123</v>
       </c>
-      <c r="H50" s="1">
+      <c r="I50" s="1">
         <v>238842</v>
       </c>
-      <c r="I50" s="1">
+      <c r="J50" s="1">
         <v>1320</v>
       </c>
-      <c r="J50" s="1">
+      <c r="K50" s="1">
         <v>528</v>
-      </c>
-      <c r="K50" s="1">
-        <v>792</v>
       </c>
       <c r="L50" s="1">
         <v>792</v>
       </c>
       <c r="M50" s="1">
+        <v>792</v>
+      </c>
+      <c r="N50" s="1">
         <v>528</v>
       </c>
-      <c r="N50" s="1">
+      <c r="O50" s="1">
         <v>6360</v>
-      </c>
-      <c r="O50" s="1">
-        <v>26398</v>
       </c>
       <c r="P50" s="1">
         <v>26398</v>
@@ -3266,8 +3414,11 @@
       <c r="Q50" s="1">
         <v>26398</v>
       </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R50" s="1">
+        <v>26398</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A51" s="6">
         <v>2025</v>
       </c>
@@ -3287,31 +3438,31 @@
         <v>16</v>
       </c>
       <c r="G51" s="1">
+        <v>40</v>
+      </c>
+      <c r="H51" s="1">
         <v>196979</v>
       </c>
-      <c r="H51" s="1">
+      <c r="I51" s="1">
         <v>219069</v>
       </c>
-      <c r="I51" s="1">
+      <c r="J51" s="1">
         <v>1214</v>
       </c>
-      <c r="J51" s="1">
+      <c r="K51" s="1">
         <v>486</v>
-      </c>
-      <c r="K51" s="1">
-        <v>729</v>
       </c>
       <c r="L51" s="1">
         <v>729</v>
       </c>
       <c r="M51" s="1">
+        <v>729</v>
+      </c>
+      <c r="N51" s="1">
         <v>486</v>
       </c>
-      <c r="N51" s="1">
+      <c r="O51" s="1">
         <v>5848</v>
-      </c>
-      <c r="O51" s="1">
-        <v>24285</v>
       </c>
       <c r="P51" s="1">
         <v>24285</v>
@@ -3319,8 +3470,11 @@
       <c r="Q51" s="1">
         <v>24285</v>
       </c>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R51" s="1">
+        <v>24285</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A52" s="6">
         <v>2025</v>
       </c>
@@ -3340,31 +3494,31 @@
         <v>15</v>
       </c>
       <c r="G52" s="1">
+        <v>36</v>
+      </c>
+      <c r="H52" s="1">
         <v>183268</v>
       </c>
-      <c r="H52" s="1">
+      <c r="I52" s="1">
         <v>204222</v>
       </c>
-      <c r="I52" s="1">
+      <c r="J52" s="1">
         <v>1129</v>
       </c>
-      <c r="J52" s="1">
+      <c r="K52" s="1">
         <v>452</v>
-      </c>
-      <c r="K52" s="1">
-        <v>678</v>
       </c>
       <c r="L52" s="1">
         <v>678</v>
       </c>
       <c r="M52" s="1">
+        <v>678</v>
+      </c>
+      <c r="N52" s="1">
         <v>452</v>
       </c>
-      <c r="N52" s="1">
+      <c r="O52" s="1">
         <v>5442</v>
-      </c>
-      <c r="O52" s="1">
-        <v>22596</v>
       </c>
       <c r="P52" s="1">
         <v>22596</v>
@@ -3372,8 +3526,11 @@
       <c r="Q52" s="1">
         <v>22596</v>
       </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R52" s="1">
+        <v>22596</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53" s="6">
         <v>2025</v>
       </c>
@@ -3393,31 +3550,31 @@
         <v>17</v>
       </c>
       <c r="G53" s="1">
+        <v>41</v>
+      </c>
+      <c r="H53" s="1">
         <v>161152</v>
       </c>
-      <c r="H53" s="1">
+      <c r="I53" s="1">
         <v>179748</v>
       </c>
-      <c r="I53" s="1">
+      <c r="J53" s="1">
         <v>993</v>
       </c>
-      <c r="J53" s="1">
+      <c r="K53" s="1">
         <v>397</v>
-      </c>
-      <c r="K53" s="1">
-        <v>596</v>
       </c>
       <c r="L53" s="1">
         <v>596</v>
       </c>
       <c r="M53" s="1">
+        <v>596</v>
+      </c>
+      <c r="N53" s="1">
         <v>397</v>
       </c>
-      <c r="N53" s="1">
+      <c r="O53" s="1">
         <v>4769</v>
-      </c>
-      <c r="O53" s="1">
-        <v>19874</v>
       </c>
       <c r="P53" s="1">
         <v>19874</v>
@@ -3425,8 +3582,11 @@
       <c r="Q53" s="1">
         <v>19874</v>
       </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R53" s="1">
+        <v>19874</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A54" s="6">
         <v>2025</v>
       </c>
@@ -3446,31 +3606,31 @@
         <v>18</v>
       </c>
       <c r="G54" s="1">
+        <v>38</v>
+      </c>
+      <c r="H54" s="1">
         <v>136784</v>
       </c>
-      <c r="H54" s="1">
+      <c r="I54" s="1">
         <v>152397</v>
       </c>
-      <c r="I54" s="1">
+      <c r="J54" s="1">
         <v>843</v>
       </c>
-      <c r="J54" s="1">
+      <c r="K54" s="1">
         <v>337</v>
-      </c>
-      <c r="K54" s="1">
-        <v>506</v>
       </c>
       <c r="L54" s="1">
         <v>506</v>
       </c>
       <c r="M54" s="1">
+        <v>506</v>
+      </c>
+      <c r="N54" s="1">
         <v>337</v>
       </c>
-      <c r="N54" s="1">
+      <c r="O54" s="1">
         <v>4049</v>
-      </c>
-      <c r="O54" s="1">
-        <v>16873</v>
       </c>
       <c r="P54" s="1">
         <v>16873</v>
@@ -3478,8 +3638,11 @@
       <c r="Q54" s="1">
         <v>16873</v>
       </c>
-    </row>
-    <row r="55" spans="1:17" s="4" customFormat="1" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R54" s="1">
+        <v>16873</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" s="4" customFormat="1" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="5" t="s">
         <v>27</v>
       </c>
@@ -3499,8 +3662,9 @@
       <c r="O55" s="5"/>
       <c r="P55" s="5"/>
       <c r="Q55" s="5"/>
-    </row>
-    <row r="56" spans="1:17" s="3" customFormat="1" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="R55" s="5"/>
+    </row>
+    <row r="56" spans="1:18" s="3" customFormat="1" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>0</v>
       </c>
@@ -3520,40 +3684,43 @@
         <v>45</v>
       </c>
       <c r="G56" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="H56" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="H56" s="2" t="s">
+      <c r="I56" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="I56" s="2" t="s">
+      <c r="J56" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="J56" s="2" t="s">
+      <c r="K56" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="K56" s="2" t="s">
+      <c r="L56" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="L56" s="2" t="s">
+      <c r="M56" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="M56" s="2" t="s">
+      <c r="N56" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="N56" s="2" t="s">
+      <c r="O56" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="O56" s="2" t="s">
+      <c r="P56" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="P56" s="2" t="s">
+      <c r="Q56" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="Q56" s="2" t="s">
+      <c r="R56" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A57" s="6">
         <v>2019</v>
       </c>
@@ -3573,31 +3740,31 @@
         <v>12</v>
       </c>
       <c r="G57" s="1">
+        <v>43</v>
+      </c>
+      <c r="H57" s="1">
         <v>49608</v>
       </c>
-      <c r="H57" s="1">
+      <c r="I57" s="1">
         <v>55120</v>
       </c>
-      <c r="I57" s="1">
+      <c r="J57" s="1">
         <v>304</v>
       </c>
-      <c r="J57" s="1">
+      <c r="K57" s="1">
         <v>122</v>
-      </c>
-      <c r="K57" s="1">
-        <v>183</v>
       </c>
       <c r="L57" s="1">
         <v>183</v>
       </c>
       <c r="M57" s="1">
+        <v>183</v>
+      </c>
+      <c r="N57" s="1">
         <v>122</v>
       </c>
-      <c r="N57" s="1">
+      <c r="O57" s="1">
         <v>1469</v>
-      </c>
-      <c r="O57" s="1">
-        <v>6120</v>
       </c>
       <c r="P57" s="1">
         <v>6120</v>
@@ -3605,8 +3772,11 @@
       <c r="Q57" s="1">
         <v>6120</v>
       </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R57" s="1">
+        <v>6120</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A58" s="6">
         <v>2019</v>
       </c>
@@ -3626,31 +3796,31 @@
         <v>11</v>
       </c>
       <c r="G58" s="1">
+        <v>42</v>
+      </c>
+      <c r="H58" s="1">
         <v>47827</v>
       </c>
-      <c r="H58" s="1">
+      <c r="I58" s="1">
         <v>53142</v>
       </c>
-      <c r="I58" s="1">
+      <c r="J58" s="1">
         <v>294</v>
       </c>
-      <c r="J58" s="1">
+      <c r="K58" s="1">
         <v>118</v>
-      </c>
-      <c r="K58" s="1">
-        <v>176</v>
       </c>
       <c r="L58" s="1">
         <v>176</v>
       </c>
       <c r="M58" s="1">
+        <v>176</v>
+      </c>
+      <c r="N58" s="1">
         <v>118</v>
       </c>
-      <c r="N58" s="1">
+      <c r="O58" s="1">
         <v>1417</v>
-      </c>
-      <c r="O58" s="1">
-        <v>5900</v>
       </c>
       <c r="P58" s="1">
         <v>5900</v>
@@ -3658,8 +3828,11 @@
       <c r="Q58" s="1">
         <v>5900</v>
       </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R58" s="1">
+        <v>5900</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A59" s="6">
         <v>2019</v>
       </c>
@@ -3679,31 +3852,31 @@
         <v>13</v>
       </c>
       <c r="G59" s="1">
+        <v>47</v>
+      </c>
+      <c r="H59" s="1">
         <v>41328</v>
       </c>
-      <c r="H59" s="1">
+      <c r="I59" s="1">
         <v>45920</v>
       </c>
-      <c r="I59" s="1">
+      <c r="J59" s="1">
         <v>254</v>
       </c>
-      <c r="J59" s="1">
+      <c r="K59" s="1">
         <v>102</v>
-      </c>
-      <c r="K59" s="1">
-        <v>153</v>
       </c>
       <c r="L59" s="1">
         <v>153</v>
       </c>
       <c r="M59" s="1">
+        <v>153</v>
+      </c>
+      <c r="N59" s="1">
         <v>102</v>
       </c>
-      <c r="N59" s="1">
+      <c r="O59" s="1">
         <v>1225</v>
-      </c>
-      <c r="O59" s="1">
-        <v>5100</v>
       </c>
       <c r="P59" s="1">
         <v>5100</v>
@@ -3711,8 +3884,11 @@
       <c r="Q59" s="1">
         <v>5100</v>
       </c>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R59" s="1">
+        <v>5100</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A60" s="6">
         <v>2019</v>
       </c>
@@ -3732,31 +3908,31 @@
         <v>12</v>
       </c>
       <c r="G60" s="1">
+        <v>44</v>
+      </c>
+      <c r="H60" s="1">
         <v>37266</v>
       </c>
-      <c r="H60" s="1">
+      <c r="I60" s="1">
         <v>41406</v>
       </c>
-      <c r="I60" s="1">
+      <c r="J60" s="1">
         <v>229</v>
       </c>
-      <c r="J60" s="1">
+      <c r="K60" s="1">
         <v>92</v>
-      </c>
-      <c r="K60" s="1">
-        <v>138</v>
       </c>
       <c r="L60" s="1">
         <v>138</v>
       </c>
       <c r="M60" s="1">
+        <v>138</v>
+      </c>
+      <c r="N60" s="1">
         <v>92</v>
       </c>
-      <c r="N60" s="1">
+      <c r="O60" s="1">
         <v>1105</v>
-      </c>
-      <c r="O60" s="1">
-        <v>4600</v>
       </c>
       <c r="P60" s="1">
         <v>4600</v>
@@ -3764,8 +3940,11 @@
       <c r="Q60" s="1">
         <v>4600</v>
       </c>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R60" s="1">
+        <v>4600</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A61" s="6">
         <v>2019</v>
       </c>
@@ -3785,31 +3964,31 @@
         <v>12</v>
       </c>
       <c r="G61" s="1">
+        <v>46</v>
+      </c>
+      <c r="H61" s="1">
         <v>33204</v>
       </c>
-      <c r="H61" s="1">
+      <c r="I61" s="1">
         <v>36960</v>
       </c>
-      <c r="I61" s="1">
+      <c r="J61" s="1">
         <v>205</v>
       </c>
-      <c r="J61" s="1">
+      <c r="K61" s="1">
         <v>82</v>
-      </c>
-      <c r="K61" s="1">
-        <v>123</v>
       </c>
       <c r="L61" s="1">
         <v>123</v>
       </c>
       <c r="M61" s="1">
+        <v>123</v>
+      </c>
+      <c r="N61" s="1">
         <v>82</v>
       </c>
-      <c r="N61" s="1">
+      <c r="O61" s="1">
         <v>984</v>
-      </c>
-      <c r="O61" s="1">
-        <v>4100</v>
       </c>
       <c r="P61" s="1">
         <v>4100</v>
@@ -3817,8 +3996,11 @@
       <c r="Q61" s="1">
         <v>4100</v>
       </c>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R61" s="1">
+        <v>4100</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A62" s="6">
         <v>2019</v>
       </c>
@@ -3838,31 +4020,31 @@
         <v>13</v>
       </c>
       <c r="G62" s="1">
+        <v>45</v>
+      </c>
+      <c r="H62" s="1">
         <v>30777</v>
       </c>
-      <c r="H62" s="1">
+      <c r="I62" s="1">
         <v>34200</v>
       </c>
-      <c r="I62" s="1">
+      <c r="J62" s="1">
         <v>189</v>
       </c>
-      <c r="J62" s="1">
+      <c r="K62" s="1">
         <v>76</v>
-      </c>
-      <c r="K62" s="1">
-        <v>114</v>
       </c>
       <c r="L62" s="1">
         <v>114</v>
       </c>
       <c r="M62" s="1">
+        <v>114</v>
+      </c>
+      <c r="N62" s="1">
         <v>76</v>
       </c>
-      <c r="N62" s="1">
+      <c r="O62" s="1">
         <v>912</v>
-      </c>
-      <c r="O62" s="1">
-        <v>3800</v>
       </c>
       <c r="P62" s="1">
         <v>3800</v>
@@ -3870,8 +4052,11 @@
       <c r="Q62" s="1">
         <v>3800</v>
       </c>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R62" s="1">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A63" s="6">
         <v>2019</v>
       </c>
@@ -3891,31 +4076,31 @@
         <v>14</v>
       </c>
       <c r="G63" s="1">
+        <v>48</v>
+      </c>
+      <c r="H63" s="1">
         <v>28349</v>
       </c>
-      <c r="H63" s="1">
+      <c r="I63" s="1">
         <v>31500</v>
       </c>
-      <c r="I63" s="1">
+      <c r="J63" s="1">
         <v>174</v>
       </c>
-      <c r="J63" s="1">
+      <c r="K63" s="1">
         <v>70</v>
-      </c>
-      <c r="K63" s="1">
-        <v>105</v>
       </c>
       <c r="L63" s="1">
         <v>105</v>
       </c>
       <c r="M63" s="1">
+        <v>105</v>
+      </c>
+      <c r="N63" s="1">
         <v>70</v>
       </c>
-      <c r="N63" s="1">
+      <c r="O63" s="1">
         <v>840</v>
-      </c>
-      <c r="O63" s="1">
-        <v>3500</v>
       </c>
       <c r="P63" s="1">
         <v>3500</v>
@@ -3923,8 +4108,11 @@
       <c r="Q63" s="1">
         <v>3500</v>
       </c>
-    </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R63" s="1">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A64" s="6">
         <v>2019</v>
       </c>
@@ -3944,31 +4132,31 @@
         <v>13</v>
       </c>
       <c r="G64" s="1">
+        <v>44</v>
+      </c>
+      <c r="H64" s="1">
         <v>25921</v>
       </c>
-      <c r="H64" s="1">
+      <c r="I64" s="1">
         <v>28800</v>
       </c>
-      <c r="I64" s="1">
+      <c r="J64" s="1">
         <v>159</v>
       </c>
-      <c r="J64" s="1">
+      <c r="K64" s="1">
         <v>64</v>
-      </c>
-      <c r="K64" s="1">
-        <v>96</v>
       </c>
       <c r="L64" s="1">
         <v>96</v>
       </c>
       <c r="M64" s="1">
+        <v>96</v>
+      </c>
+      <c r="N64" s="1">
         <v>64</v>
       </c>
-      <c r="N64" s="1">
+      <c r="O64" s="1">
         <v>768</v>
-      </c>
-      <c r="O64" s="1">
-        <v>3200</v>
       </c>
       <c r="P64" s="1">
         <v>3200</v>
@@ -3976,8 +4164,11 @@
       <c r="Q64" s="1">
         <v>3200</v>
       </c>
-    </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R64" s="1">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A65" s="6">
         <v>2019</v>
       </c>
@@ -3997,31 +4188,31 @@
         <v>14</v>
       </c>
       <c r="G65" s="1">
+        <v>42</v>
+      </c>
+      <c r="H65" s="1">
         <v>23493</v>
       </c>
-      <c r="H65" s="1">
+      <c r="I65" s="1">
         <v>26100</v>
       </c>
-      <c r="I65" s="1">
+      <c r="J65" s="1">
         <v>145</v>
       </c>
-      <c r="J65" s="1">
+      <c r="K65" s="1">
         <v>58</v>
-      </c>
-      <c r="K65" s="1">
-        <v>87</v>
       </c>
       <c r="L65" s="1">
         <v>87</v>
       </c>
       <c r="M65" s="1">
+        <v>87</v>
+      </c>
+      <c r="N65" s="1">
         <v>58</v>
       </c>
-      <c r="N65" s="1">
+      <c r="O65" s="1">
         <v>696</v>
-      </c>
-      <c r="O65" s="1">
-        <v>2900</v>
       </c>
       <c r="P65" s="1">
         <v>2900</v>
@@ -4029,8 +4220,11 @@
       <c r="Q65" s="1">
         <v>2900</v>
       </c>
-    </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R65" s="1">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A66" s="6">
         <v>2019</v>
       </c>
@@ -4050,31 +4244,31 @@
         <v>15</v>
       </c>
       <c r="G66" s="1">
+        <v>41</v>
+      </c>
+      <c r="H66" s="1">
         <v>17010</v>
       </c>
-      <c r="H66" s="1">
+      <c r="I66" s="1">
         <v>18900</v>
       </c>
-      <c r="I66" s="1">
+      <c r="J66" s="1">
         <v>105</v>
       </c>
-      <c r="J66" s="1">
+      <c r="K66" s="1">
         <v>42</v>
-      </c>
-      <c r="K66" s="1">
-        <v>63</v>
       </c>
       <c r="L66" s="1">
         <v>63</v>
       </c>
       <c r="M66" s="1">
+        <v>63</v>
+      </c>
+      <c r="N66" s="1">
         <v>42</v>
       </c>
-      <c r="N66" s="1">
+      <c r="O66" s="1">
         <v>504</v>
-      </c>
-      <c r="O66" s="1">
-        <v>2100</v>
       </c>
       <c r="P66" s="1">
         <v>2100</v>
@@ -4082,8 +4276,11 @@
       <c r="Q66" s="1">
         <v>2100</v>
       </c>
-    </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R66" s="1">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A67" s="6">
         <v>2019</v>
       </c>
@@ -4103,31 +4300,31 @@
         <v>14</v>
       </c>
       <c r="G67" s="1">
+        <v>43</v>
+      </c>
+      <c r="H67" s="1">
         <v>15393</v>
       </c>
-      <c r="H67" s="1">
+      <c r="I67" s="1">
         <v>17100</v>
       </c>
-      <c r="I67" s="1">
+      <c r="J67" s="1">
         <v>95</v>
       </c>
-      <c r="J67" s="1">
+      <c r="K67" s="1">
         <v>38</v>
-      </c>
-      <c r="K67" s="1">
-        <v>57</v>
       </c>
       <c r="L67" s="1">
         <v>57</v>
       </c>
       <c r="M67" s="1">
+        <v>57</v>
+      </c>
+      <c r="N67" s="1">
         <v>38</v>
       </c>
-      <c r="N67" s="1">
+      <c r="O67" s="1">
         <v>456</v>
-      </c>
-      <c r="O67" s="1">
-        <v>1900</v>
       </c>
       <c r="P67" s="1">
         <v>1900</v>
@@ -4135,8 +4332,11 @@
       <c r="Q67" s="1">
         <v>1900</v>
       </c>
-    </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R67" s="1">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A68" s="6">
         <v>2019</v>
       </c>
@@ -4156,31 +4356,31 @@
         <v>16</v>
       </c>
       <c r="G68" s="1">
+        <v>40</v>
+      </c>
+      <c r="H68" s="1">
         <v>13209</v>
       </c>
-      <c r="H68" s="1">
+      <c r="I68" s="1">
         <v>14676</v>
       </c>
-      <c r="I68" s="1">
+      <c r="J68" s="1">
         <v>81</v>
       </c>
-      <c r="J68" s="1">
+      <c r="K68" s="1">
         <v>33</v>
-      </c>
-      <c r="K68" s="1">
-        <v>49</v>
       </c>
       <c r="L68" s="1">
         <v>49</v>
       </c>
       <c r="M68" s="1">
+        <v>49</v>
+      </c>
+      <c r="N68" s="1">
         <v>33</v>
       </c>
-      <c r="N68" s="1">
+      <c r="O68" s="1">
         <v>391</v>
-      </c>
-      <c r="O68" s="1">
-        <v>1631</v>
       </c>
       <c r="P68" s="1">
         <v>1631</v>
@@ -4188,8 +4388,11 @@
       <c r="Q68" s="1">
         <v>1631</v>
       </c>
-    </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R68" s="1">
+        <v>1631</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A69" s="6">
         <v>2019</v>
       </c>
@@ -4209,31 +4412,31 @@
         <v>17</v>
       </c>
       <c r="G69" s="1">
+        <v>39</v>
+      </c>
+      <c r="H69" s="1">
         <v>8916</v>
       </c>
-      <c r="H69" s="1">
+      <c r="I69" s="1">
         <v>9900</v>
       </c>
-      <c r="I69" s="1">
+      <c r="J69" s="1">
         <v>55</v>
       </c>
-      <c r="J69" s="1">
+      <c r="K69" s="1">
         <v>22</v>
-      </c>
-      <c r="K69" s="1">
-        <v>33</v>
       </c>
       <c r="L69" s="1">
         <v>33</v>
       </c>
       <c r="M69" s="1">
+        <v>33</v>
+      </c>
+      <c r="N69" s="1">
         <v>22</v>
       </c>
-      <c r="N69" s="1">
+      <c r="O69" s="1">
         <v>264</v>
-      </c>
-      <c r="O69" s="1">
-        <v>1100</v>
       </c>
       <c r="P69" s="1">
         <v>1100</v>
@@ -4241,8 +4444,11 @@
       <c r="Q69" s="1">
         <v>1100</v>
       </c>
-    </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R69" s="1">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A70" s="6">
         <v>2021</v>
       </c>
@@ -4262,31 +4468,31 @@
         <v>12</v>
       </c>
       <c r="G70" s="1">
+        <v>44</v>
+      </c>
+      <c r="H70" s="1">
         <v>136836</v>
       </c>
-      <c r="H70" s="1">
+      <c r="I70" s="1">
         <v>152016</v>
       </c>
-      <c r="I70" s="1">
+      <c r="J70" s="1">
         <v>843</v>
       </c>
-      <c r="J70" s="1">
+      <c r="K70" s="1">
         <v>337</v>
-      </c>
-      <c r="K70" s="1">
-        <v>506</v>
       </c>
       <c r="L70" s="1">
         <v>506</v>
       </c>
       <c r="M70" s="1">
+        <v>506</v>
+      </c>
+      <c r="N70" s="1">
         <v>337</v>
       </c>
-      <c r="N70" s="1">
+      <c r="O70" s="1">
         <v>4041</v>
-      </c>
-      <c r="O70" s="1">
-        <v>16890</v>
       </c>
       <c r="P70" s="1">
         <v>16890</v>
@@ -4294,8 +4500,11 @@
       <c r="Q70" s="1">
         <v>16890</v>
       </c>
-    </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R70" s="1">
+        <v>16890</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A71" s="6">
         <v>2021</v>
       </c>
@@ -4315,31 +4524,31 @@
         <v>13</v>
       </c>
       <c r="G71" s="1">
+        <v>46</v>
+      </c>
+      <c r="H71" s="1">
         <v>123482</v>
       </c>
-      <c r="H71" s="1">
+      <c r="I71" s="1">
         <v>137172</v>
       </c>
-      <c r="I71" s="1">
+      <c r="J71" s="1">
         <v>762</v>
       </c>
-      <c r="J71" s="1">
+      <c r="K71" s="1">
         <v>305</v>
-      </c>
-      <c r="K71" s="1">
-        <v>457</v>
       </c>
       <c r="L71" s="1">
         <v>457</v>
       </c>
       <c r="M71" s="1">
+        <v>457</v>
+      </c>
+      <c r="N71" s="1">
         <v>305</v>
       </c>
-      <c r="N71" s="1">
+      <c r="O71" s="1">
         <v>3646</v>
-      </c>
-      <c r="O71" s="1">
-        <v>15240</v>
       </c>
       <c r="P71" s="1">
         <v>15240</v>
@@ -4347,8 +4556,11 @@
       <c r="Q71" s="1">
         <v>15240</v>
       </c>
-    </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R71" s="1">
+        <v>15240</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A72" s="6">
         <v>2021</v>
       </c>
@@ -4368,31 +4580,31 @@
         <v>12</v>
       </c>
       <c r="G72" s="1">
+        <v>48</v>
+      </c>
+      <c r="H72" s="1">
         <v>120725</v>
       </c>
-      <c r="H72" s="1">
+      <c r="I72" s="1">
         <v>134100</v>
       </c>
-      <c r="I72" s="1">
+      <c r="J72" s="1">
         <v>745</v>
       </c>
-      <c r="J72" s="1">
+      <c r="K72" s="1">
         <v>298</v>
-      </c>
-      <c r="K72" s="1">
-        <v>447</v>
       </c>
       <c r="L72" s="1">
         <v>447</v>
       </c>
       <c r="M72" s="1">
+        <v>447</v>
+      </c>
+      <c r="N72" s="1">
         <v>298</v>
       </c>
-      <c r="N72" s="1">
+      <c r="O72" s="1">
         <v>3564</v>
-      </c>
-      <c r="O72" s="1">
-        <v>14900</v>
       </c>
       <c r="P72" s="1">
         <v>14900</v>
@@ -4400,8 +4612,11 @@
       <c r="Q72" s="1">
         <v>14900</v>
       </c>
-    </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R72" s="1">
+        <v>14900</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A73" s="6">
         <v>2021</v>
       </c>
@@ -4421,31 +4636,31 @@
         <v>12</v>
       </c>
       <c r="G73" s="1">
+        <v>43</v>
+      </c>
+      <c r="H73" s="1">
         <v>98438</v>
       </c>
-      <c r="H73" s="1">
+      <c r="I73" s="1">
         <v>109350</v>
       </c>
-      <c r="I73" s="1">
+      <c r="J73" s="1">
         <v>608</v>
       </c>
-      <c r="J73" s="1">
+      <c r="K73" s="1">
         <v>243</v>
-      </c>
-      <c r="K73" s="1">
-        <v>365</v>
       </c>
       <c r="L73" s="1">
         <v>365</v>
       </c>
       <c r="M73" s="1">
+        <v>365</v>
+      </c>
+      <c r="N73" s="1">
         <v>243</v>
       </c>
-      <c r="N73" s="1">
+      <c r="O73" s="1">
         <v>2907</v>
-      </c>
-      <c r="O73" s="1">
-        <v>12150</v>
       </c>
       <c r="P73" s="1">
         <v>12150</v>
@@ -4453,8 +4668,11 @@
       <c r="Q73" s="1">
         <v>12150</v>
       </c>
-    </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R73" s="1">
+        <v>12150</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A74" s="6">
         <v>2021</v>
       </c>
@@ -4474,31 +4692,31 @@
         <v>12</v>
       </c>
       <c r="G74" s="1">
+        <v>45</v>
+      </c>
+      <c r="H74" s="1">
         <v>89308</v>
       </c>
-      <c r="H74" s="1">
+      <c r="I74" s="1">
         <v>99180</v>
       </c>
-      <c r="I74" s="1">
+      <c r="J74" s="1">
         <v>552</v>
       </c>
-      <c r="J74" s="1">
+      <c r="K74" s="1">
         <v>221</v>
-      </c>
-      <c r="K74" s="1">
-        <v>331</v>
       </c>
       <c r="L74" s="1">
         <v>331</v>
       </c>
       <c r="M74" s="1">
+        <v>331</v>
+      </c>
+      <c r="N74" s="1">
         <v>221</v>
       </c>
-      <c r="N74" s="1">
+      <c r="O74" s="1">
         <v>2639</v>
-      </c>
-      <c r="O74" s="1">
-        <v>11020</v>
       </c>
       <c r="P74" s="1">
         <v>11020</v>
@@ -4506,8 +4724,11 @@
       <c r="Q74" s="1">
         <v>11020</v>
       </c>
-    </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R74" s="1">
+        <v>11020</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A75" s="6">
         <v>2021</v>
       </c>
@@ -4527,31 +4748,31 @@
         <v>13</v>
       </c>
       <c r="G75" s="1">
+        <v>47</v>
+      </c>
+      <c r="H75" s="1">
         <v>79338</v>
       </c>
-      <c r="H75" s="1">
+      <c r="I75" s="1">
         <v>88200</v>
       </c>
-      <c r="I75" s="1">
+      <c r="J75" s="1">
         <v>490</v>
       </c>
-      <c r="J75" s="1">
+      <c r="K75" s="1">
         <v>196</v>
-      </c>
-      <c r="K75" s="1">
-        <v>294</v>
       </c>
       <c r="L75" s="1">
         <v>294</v>
       </c>
       <c r="M75" s="1">
+        <v>294</v>
+      </c>
+      <c r="N75" s="1">
         <v>196</v>
       </c>
-      <c r="N75" s="1">
+      <c r="O75" s="1">
         <v>2345</v>
-      </c>
-      <c r="O75" s="1">
-        <v>9800</v>
       </c>
       <c r="P75" s="1">
         <v>9800</v>
@@ -4559,8 +4780,11 @@
       <c r="Q75" s="1">
         <v>9800</v>
       </c>
-    </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R75" s="1">
+        <v>9800</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A76" s="6">
         <v>2021</v>
       </c>
@@ -4580,31 +4804,31 @@
         <v>14</v>
       </c>
       <c r="G76" s="1">
+        <v>44</v>
+      </c>
+      <c r="H76" s="1">
         <v>73024</v>
       </c>
-      <c r="H76" s="1">
+      <c r="I76" s="1">
         <v>81180</v>
       </c>
-      <c r="I76" s="1">
+      <c r="J76" s="1">
         <v>451</v>
       </c>
-      <c r="J76" s="1">
+      <c r="K76" s="1">
         <v>180</v>
-      </c>
-      <c r="K76" s="1">
-        <v>270</v>
       </c>
       <c r="L76" s="1">
         <v>270</v>
       </c>
       <c r="M76" s="1">
+        <v>270</v>
+      </c>
+      <c r="N76" s="1">
         <v>180</v>
       </c>
-      <c r="N76" s="1">
+      <c r="O76" s="1">
         <v>2158</v>
-      </c>
-      <c r="O76" s="1">
-        <v>9020</v>
       </c>
       <c r="P76" s="1">
         <v>9020</v>
@@ -4612,8 +4836,11 @@
       <c r="Q76" s="1">
         <v>9020</v>
       </c>
-    </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R76" s="1">
+        <v>9020</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A77" s="6">
         <v>2021</v>
       </c>
@@ -4633,31 +4860,31 @@
         <v>13</v>
       </c>
       <c r="G77" s="1">
+        <v>49</v>
+      </c>
+      <c r="H77" s="1">
         <v>68389</v>
       </c>
-      <c r="H77" s="1">
+      <c r="I77" s="1">
         <v>76050</v>
       </c>
-      <c r="I77" s="1">
+      <c r="J77" s="1">
         <v>423</v>
       </c>
-      <c r="J77" s="1">
+      <c r="K77" s="1">
         <v>169</v>
-      </c>
-      <c r="K77" s="1">
-        <v>254</v>
       </c>
       <c r="L77" s="1">
         <v>254</v>
       </c>
       <c r="M77" s="1">
+        <v>254</v>
+      </c>
+      <c r="N77" s="1">
         <v>169</v>
       </c>
-      <c r="N77" s="1">
+      <c r="O77" s="1">
         <v>2021</v>
-      </c>
-      <c r="O77" s="1">
-        <v>8450</v>
       </c>
       <c r="P77" s="1">
         <v>8450</v>
@@ -4665,8 +4892,11 @@
       <c r="Q77" s="1">
         <v>8450</v>
       </c>
-    </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R77" s="1">
+        <v>8450</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A78" s="6">
         <v>2021</v>
       </c>
@@ -4686,31 +4916,31 @@
         <v>14</v>
       </c>
       <c r="G78" s="1">
+        <v>45</v>
+      </c>
+      <c r="H78" s="1">
         <v>62370</v>
       </c>
-      <c r="H78" s="1">
+      <c r="I78" s="1">
         <v>69300</v>
       </c>
-      <c r="I78" s="1">
+      <c r="J78" s="1">
         <v>385</v>
       </c>
-      <c r="J78" s="1">
+      <c r="K78" s="1">
         <v>154</v>
-      </c>
-      <c r="K78" s="1">
-        <v>231</v>
       </c>
       <c r="L78" s="1">
         <v>231</v>
       </c>
       <c r="M78" s="1">
+        <v>231</v>
+      </c>
+      <c r="N78" s="1">
         <v>154</v>
       </c>
-      <c r="N78" s="1">
+      <c r="O78" s="1">
         <v>1843</v>
-      </c>
-      <c r="O78" s="1">
-        <v>7700</v>
       </c>
       <c r="P78" s="1">
         <v>7700</v>
@@ -4718,8 +4948,11 @@
       <c r="Q78" s="1">
         <v>7700</v>
       </c>
-    </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R78" s="1">
+        <v>7700</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A79" s="6">
         <v>2021</v>
       </c>
@@ -4739,31 +4972,31 @@
         <v>15</v>
       </c>
       <c r="G79" s="1">
+        <v>43</v>
+      </c>
+      <c r="H79" s="1">
         <v>42168</v>
       </c>
-      <c r="H79" s="1">
+      <c r="I79" s="1">
         <v>46800</v>
       </c>
-      <c r="I79" s="1">
+      <c r="J79" s="1">
         <v>260</v>
       </c>
-      <c r="J79" s="1">
+      <c r="K79" s="1">
         <v>104</v>
-      </c>
-      <c r="K79" s="1">
-        <v>156</v>
       </c>
       <c r="L79" s="1">
         <v>156</v>
       </c>
       <c r="M79" s="1">
+        <v>156</v>
+      </c>
+      <c r="N79" s="1">
         <v>104</v>
       </c>
-      <c r="N79" s="1">
+      <c r="O79" s="1">
         <v>1245</v>
-      </c>
-      <c r="O79" s="1">
-        <v>5200</v>
       </c>
       <c r="P79" s="1">
         <v>5200</v>
@@ -4771,8 +5004,11 @@
       <c r="Q79" s="1">
         <v>5200</v>
       </c>
-    </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R79" s="1">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A80" s="6">
         <v>2021</v>
       </c>
@@ -4792,31 +5028,31 @@
         <v>14</v>
       </c>
       <c r="G80" s="1">
+        <v>41</v>
+      </c>
+      <c r="H80" s="1">
         <v>34849</v>
       </c>
-      <c r="H80" s="1">
+      <c r="I80" s="1">
         <v>38700</v>
       </c>
-      <c r="I80" s="1">
+      <c r="J80" s="1">
         <v>215</v>
       </c>
-      <c r="J80" s="1">
+      <c r="K80" s="1">
         <v>86</v>
-      </c>
-      <c r="K80" s="1">
-        <v>129</v>
       </c>
       <c r="L80" s="1">
         <v>129</v>
       </c>
       <c r="M80" s="1">
+        <v>129</v>
+      </c>
+      <c r="N80" s="1">
         <v>86</v>
       </c>
-      <c r="N80" s="1">
+      <c r="O80" s="1">
         <v>1030</v>
-      </c>
-      <c r="O80" s="1">
-        <v>4300</v>
       </c>
       <c r="P80" s="1">
         <v>4300</v>
@@ -4824,8 +5060,11 @@
       <c r="Q80" s="1">
         <v>4300</v>
       </c>
-    </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R80" s="1">
+        <v>4300</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A81" s="6">
         <v>2021</v>
       </c>
@@ -4845,31 +5084,31 @@
         <v>16</v>
       </c>
       <c r="G81" s="1">
+        <v>42</v>
+      </c>
+      <c r="H81" s="1">
         <v>25296</v>
       </c>
-      <c r="H81" s="1">
+      <c r="I81" s="1">
         <v>28080</v>
       </c>
-      <c r="I81" s="1">
+      <c r="J81" s="1">
         <v>156</v>
       </c>
-      <c r="J81" s="1">
+      <c r="K81" s="1">
         <v>62</v>
-      </c>
-      <c r="K81" s="1">
-        <v>93</v>
       </c>
       <c r="L81" s="1">
         <v>93</v>
       </c>
       <c r="M81" s="1">
+        <v>93</v>
+      </c>
+      <c r="N81" s="1">
         <v>62</v>
       </c>
-      <c r="N81" s="1">
+      <c r="O81" s="1">
         <v>748</v>
-      </c>
-      <c r="O81" s="1">
-        <v>3120</v>
       </c>
       <c r="P81" s="1">
         <v>3120</v>
@@ -4877,8 +5116,11 @@
       <c r="Q81" s="1">
         <v>3120</v>
       </c>
-    </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R81" s="1">
+        <v>3120</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A82" s="6">
         <v>2021</v>
       </c>
@@ -4898,31 +5140,31 @@
         <v>17</v>
       </c>
       <c r="G82" s="1">
+        <v>39</v>
+      </c>
+      <c r="H82" s="1">
         <v>11997</v>
       </c>
-      <c r="H82" s="1">
+      <c r="I82" s="1">
         <v>13320</v>
       </c>
-      <c r="I82" s="1">
+      <c r="J82" s="1">
         <v>74</v>
       </c>
-      <c r="J82" s="1">
+      <c r="K82" s="1">
         <v>30</v>
-      </c>
-      <c r="K82" s="1">
-        <v>44</v>
       </c>
       <c r="L82" s="1">
         <v>44</v>
       </c>
       <c r="M82" s="1">
+        <v>44</v>
+      </c>
+      <c r="N82" s="1">
         <v>30</v>
       </c>
-      <c r="N82" s="1">
+      <c r="O82" s="1">
         <v>355</v>
-      </c>
-      <c r="O82" s="1">
-        <v>1480</v>
       </c>
       <c r="P82" s="1">
         <v>1480</v>
@@ -4930,8 +5172,11 @@
       <c r="Q82" s="1">
         <v>1480</v>
       </c>
-    </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R82" s="1">
+        <v>1480</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A83" s="6">
         <v>2024</v>
       </c>
@@ -4951,31 +5196,31 @@
         <v>13</v>
       </c>
       <c r="G83" s="1">
+        <v>46</v>
+      </c>
+      <c r="H83" s="1">
         <v>52056</v>
       </c>
-      <c r="H83" s="1">
+      <c r="I83" s="1">
         <v>57960</v>
       </c>
-      <c r="I83" s="1">
+      <c r="J83" s="1">
         <v>321</v>
       </c>
-      <c r="J83" s="1">
+      <c r="K83" s="1">
         <v>128</v>
-      </c>
-      <c r="K83" s="1">
-        <v>192</v>
       </c>
       <c r="L83" s="1">
         <v>192</v>
       </c>
       <c r="M83" s="1">
+        <v>192</v>
+      </c>
+      <c r="N83" s="1">
         <v>128</v>
       </c>
-      <c r="N83" s="1">
+      <c r="O83" s="1">
         <v>1540</v>
-      </c>
-      <c r="O83" s="1">
-        <v>6420</v>
       </c>
       <c r="P83" s="1">
         <v>6420</v>
@@ -4983,8 +5228,11 @@
       <c r="Q83" s="1">
         <v>6420</v>
       </c>
-    </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R83" s="1">
+        <v>6420</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A84" s="6">
         <v>2024</v>
       </c>
@@ -5004,31 +5252,31 @@
         <v>12</v>
       </c>
       <c r="G84" s="1">
+        <v>44</v>
+      </c>
+      <c r="H84" s="1">
         <v>50112</v>
       </c>
-      <c r="H84" s="1">
+      <c r="I84" s="1">
         <v>55710</v>
       </c>
-      <c r="I84" s="1">
+      <c r="J84" s="1">
         <v>309</v>
       </c>
-      <c r="J84" s="1">
+      <c r="K84" s="1">
         <v>124</v>
-      </c>
-      <c r="K84" s="1">
-        <v>185</v>
       </c>
       <c r="L84" s="1">
         <v>185</v>
       </c>
       <c r="M84" s="1">
+        <v>185</v>
+      </c>
+      <c r="N84" s="1">
         <v>124</v>
       </c>
-      <c r="N84" s="1">
+      <c r="O84" s="1">
         <v>1482</v>
-      </c>
-      <c r="O84" s="1">
-        <v>6180</v>
       </c>
       <c r="P84" s="1">
         <v>6180</v>
@@ -5036,8 +5284,11 @@
       <c r="Q84" s="1">
         <v>6180</v>
       </c>
-    </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R84" s="1">
+        <v>6180</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A85" s="6">
         <v>2024</v>
       </c>
@@ -5057,31 +5308,31 @@
         <v>12</v>
       </c>
       <c r="G85" s="1">
+        <v>42</v>
+      </c>
+      <c r="H85" s="1">
         <v>41539</v>
       </c>
-      <c r="H85" s="1">
+      <c r="I85" s="1">
         <v>46176</v>
       </c>
-      <c r="I85" s="1">
+      <c r="J85" s="1">
         <v>256</v>
       </c>
-      <c r="J85" s="1">
+      <c r="K85" s="1">
         <v>102</v>
-      </c>
-      <c r="K85" s="1">
-        <v>153</v>
       </c>
       <c r="L85" s="1">
         <v>153</v>
       </c>
       <c r="M85" s="1">
+        <v>153</v>
+      </c>
+      <c r="N85" s="1">
         <v>102</v>
       </c>
-      <c r="N85" s="1">
+      <c r="O85" s="1">
         <v>1227</v>
-      </c>
-      <c r="O85" s="1">
-        <v>5120</v>
       </c>
       <c r="P85" s="1">
         <v>5120</v>
@@ -5089,8 +5340,11 @@
       <c r="Q85" s="1">
         <v>5120</v>
       </c>
-    </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R85" s="1">
+        <v>5120</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A86" s="6">
         <v>2024</v>
       </c>
@@ -5110,31 +5364,31 @@
         <v>13</v>
       </c>
       <c r="G86" s="1">
+        <v>43</v>
+      </c>
+      <c r="H86" s="1">
         <v>38220</v>
       </c>
-      <c r="H86" s="1">
+      <c r="I86" s="1">
         <v>42480</v>
       </c>
-      <c r="I86" s="1">
+      <c r="J86" s="1">
         <v>235</v>
       </c>
-      <c r="J86" s="1">
+      <c r="K86" s="1">
         <v>94</v>
-      </c>
-      <c r="K86" s="1">
-        <v>141</v>
       </c>
       <c r="L86" s="1">
         <v>141</v>
       </c>
       <c r="M86" s="1">
+        <v>141</v>
+      </c>
+      <c r="N86" s="1">
         <v>94</v>
       </c>
-      <c r="N86" s="1">
+      <c r="O86" s="1">
         <v>1130</v>
-      </c>
-      <c r="O86" s="1">
-        <v>4710</v>
       </c>
       <c r="P86" s="1">
         <v>4710</v>
@@ -5142,8 +5396,11 @@
       <c r="Q86" s="1">
         <v>4710</v>
       </c>
-    </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R86" s="1">
+        <v>4710</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A87" s="6">
         <v>2024</v>
       </c>
@@ -5163,31 +5420,31 @@
         <v>12</v>
       </c>
       <c r="G87" s="1">
+        <v>47</v>
+      </c>
+      <c r="H87" s="1">
         <v>31824</v>
       </c>
-      <c r="H87" s="1">
+      <c r="I87" s="1">
         <v>35328</v>
       </c>
-      <c r="I87" s="1">
+      <c r="J87" s="1">
         <v>196</v>
       </c>
-      <c r="J87" s="1">
+      <c r="K87" s="1">
         <v>78</v>
-      </c>
-      <c r="K87" s="1">
-        <v>118</v>
       </c>
       <c r="L87" s="1">
         <v>118</v>
       </c>
       <c r="M87" s="1">
+        <v>118</v>
+      </c>
+      <c r="N87" s="1">
         <v>78</v>
       </c>
-      <c r="N87" s="1">
+      <c r="O87" s="1">
         <v>941</v>
-      </c>
-      <c r="O87" s="1">
-        <v>3920</v>
       </c>
       <c r="P87" s="1">
         <v>3920</v>
@@ -5195,8 +5452,11 @@
       <c r="Q87" s="1">
         <v>3920</v>
       </c>
-    </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R87" s="1">
+        <v>3920</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A88" s="6">
         <v>2024</v>
       </c>
@@ -5216,31 +5476,31 @@
         <v>13</v>
       </c>
       <c r="G88" s="1">
+        <v>45</v>
+      </c>
+      <c r="H88" s="1">
         <v>27189</v>
       </c>
-      <c r="H88" s="1">
+      <c r="I88" s="1">
         <v>30150</v>
       </c>
-      <c r="I88" s="1">
+      <c r="J88" s="1">
         <v>167</v>
       </c>
-      <c r="J88" s="1">
+      <c r="K88" s="1">
         <v>67</v>
-      </c>
-      <c r="K88" s="1">
-        <v>100</v>
       </c>
       <c r="L88" s="1">
         <v>100</v>
       </c>
       <c r="M88" s="1">
+        <v>100</v>
+      </c>
+      <c r="N88" s="1">
         <v>67</v>
       </c>
-      <c r="N88" s="1">
+      <c r="O88" s="1">
         <v>806</v>
-      </c>
-      <c r="O88" s="1">
-        <v>3350</v>
       </c>
       <c r="P88" s="1">
         <v>3350</v>
@@ -5248,8 +5508,11 @@
       <c r="Q88" s="1">
         <v>3350</v>
       </c>
-    </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R88" s="1">
+        <v>3350</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A89" s="6">
         <v>2024</v>
       </c>
@@ -5269,31 +5532,31 @@
         <v>14</v>
       </c>
       <c r="G89" s="1">
+        <v>48</v>
+      </c>
+      <c r="H89" s="1">
         <v>24430</v>
       </c>
-      <c r="H89" s="1">
+      <c r="I89" s="1">
         <v>27180</v>
       </c>
-      <c r="I89" s="1">
+      <c r="J89" s="1">
         <v>150</v>
       </c>
-      <c r="J89" s="1">
+      <c r="K89" s="1">
         <v>60</v>
-      </c>
-      <c r="K89" s="1">
-        <v>90</v>
       </c>
       <c r="L89" s="1">
         <v>90</v>
       </c>
       <c r="M89" s="1">
+        <v>90</v>
+      </c>
+      <c r="N89" s="1">
         <v>60</v>
       </c>
-      <c r="N89" s="1">
+      <c r="O89" s="1">
         <v>724</v>
-      </c>
-      <c r="O89" s="1">
-        <v>3010</v>
       </c>
       <c r="P89" s="1">
         <v>3010</v>
@@ -5301,8 +5564,11 @@
       <c r="Q89" s="1">
         <v>3010</v>
       </c>
-    </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R89" s="1">
+        <v>3010</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A90" s="6">
         <v>2024</v>
       </c>
@@ -5322,31 +5588,31 @@
         <v>13</v>
       </c>
       <c r="G90" s="1">
+        <v>44</v>
+      </c>
+      <c r="H90" s="1">
         <v>22561</v>
       </c>
-      <c r="H90" s="1">
+      <c r="I90" s="1">
         <v>25020</v>
       </c>
-      <c r="I90" s="1">
+      <c r="J90" s="1">
         <v>139</v>
       </c>
-      <c r="J90" s="1">
+      <c r="K90" s="1">
         <v>56</v>
-      </c>
-      <c r="K90" s="1">
-        <v>83</v>
       </c>
       <c r="L90" s="1">
         <v>83</v>
       </c>
       <c r="M90" s="1">
+        <v>83</v>
+      </c>
+      <c r="N90" s="1">
         <v>56</v>
       </c>
-      <c r="N90" s="1">
+      <c r="O90" s="1">
         <v>668</v>
-      </c>
-      <c r="O90" s="1">
-        <v>2780</v>
       </c>
       <c r="P90" s="1">
         <v>2780</v>
@@ -5354,8 +5620,11 @@
       <c r="Q90" s="1">
         <v>2780</v>
       </c>
-    </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R90" s="1">
+        <v>2780</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A91" s="6">
         <v>2024</v>
       </c>
@@ -5375,31 +5644,31 @@
         <v>14</v>
       </c>
       <c r="G91" s="1">
+        <v>42</v>
+      </c>
+      <c r="H91" s="1">
         <v>20298</v>
       </c>
-      <c r="H91" s="1">
+      <c r="I91" s="1">
         <v>22500</v>
       </c>
-      <c r="I91" s="1">
+      <c r="J91" s="1">
         <v>125</v>
       </c>
-      <c r="J91" s="1">
+      <c r="K91" s="1">
         <v>50</v>
-      </c>
-      <c r="K91" s="1">
-        <v>75</v>
       </c>
       <c r="L91" s="1">
         <v>75</v>
       </c>
       <c r="M91" s="1">
+        <v>75</v>
+      </c>
+      <c r="N91" s="1">
         <v>50</v>
       </c>
-      <c r="N91" s="1">
+      <c r="O91" s="1">
         <v>600</v>
-      </c>
-      <c r="O91" s="1">
-        <v>2500</v>
       </c>
       <c r="P91" s="1">
         <v>2500</v>
@@ -5407,8 +5676,11 @@
       <c r="Q91" s="1">
         <v>2500</v>
       </c>
-    </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R91" s="1">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A92" s="6">
         <v>2024</v>
       </c>
@@ -5428,31 +5700,31 @@
         <v>15</v>
       </c>
       <c r="G92" s="1">
+        <v>40</v>
+      </c>
+      <c r="H92" s="1">
         <v>15417</v>
       </c>
-      <c r="H92" s="1">
+      <c r="I92" s="1">
         <v>17100</v>
       </c>
-      <c r="I92" s="1">
+      <c r="J92" s="1">
         <v>95</v>
       </c>
-      <c r="J92" s="1">
+      <c r="K92" s="1">
         <v>38</v>
-      </c>
-      <c r="K92" s="1">
-        <v>57</v>
       </c>
       <c r="L92" s="1">
         <v>57</v>
       </c>
       <c r="M92" s="1">
+        <v>57</v>
+      </c>
+      <c r="N92" s="1">
         <v>38</v>
       </c>
-      <c r="N92" s="1">
+      <c r="O92" s="1">
         <v>456</v>
-      </c>
-      <c r="O92" s="1">
-        <v>1900</v>
       </c>
       <c r="P92" s="1">
         <v>1900</v>
@@ -5460,8 +5732,11 @@
       <c r="Q92" s="1">
         <v>1900</v>
       </c>
-    </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R92" s="1">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A93" s="6">
         <v>2024</v>
       </c>
@@ -5481,31 +5756,31 @@
         <v>14</v>
       </c>
       <c r="G93" s="1">
+        <v>41</v>
+      </c>
+      <c r="H93" s="1">
         <v>14199</v>
       </c>
-      <c r="H93" s="1">
+      <c r="I93" s="1">
         <v>15750</v>
       </c>
-      <c r="I93" s="1">
+      <c r="J93" s="1">
         <v>87</v>
       </c>
-      <c r="J93" s="1">
+      <c r="K93" s="1">
         <v>35</v>
-      </c>
-      <c r="K93" s="1">
-        <v>52</v>
       </c>
       <c r="L93" s="1">
         <v>52</v>
       </c>
       <c r="M93" s="1">
+        <v>52</v>
+      </c>
+      <c r="N93" s="1">
         <v>35</v>
       </c>
-      <c r="N93" s="1">
+      <c r="O93" s="1">
         <v>420</v>
-      </c>
-      <c r="O93" s="1">
-        <v>1750</v>
       </c>
       <c r="P93" s="1">
         <v>1750</v>
@@ -5513,8 +5788,11 @@
       <c r="Q93" s="1">
         <v>1750</v>
       </c>
-    </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R93" s="1">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A94" s="6">
         <v>2024</v>
       </c>
@@ -5534,31 +5812,31 @@
         <v>16</v>
       </c>
       <c r="G94" s="1">
+        <v>38</v>
+      </c>
+      <c r="H94" s="1">
         <v>12010</v>
       </c>
-      <c r="H94" s="1">
+      <c r="I94" s="1">
         <v>13329</v>
       </c>
-      <c r="I94" s="1">
+      <c r="J94" s="1">
         <v>74</v>
       </c>
-      <c r="J94" s="1">
+      <c r="K94" s="1">
         <v>30</v>
-      </c>
-      <c r="K94" s="1">
-        <v>44</v>
       </c>
       <c r="L94" s="1">
         <v>44</v>
       </c>
       <c r="M94" s="1">
+        <v>44</v>
+      </c>
+      <c r="N94" s="1">
         <v>30</v>
       </c>
-      <c r="N94" s="1">
+      <c r="O94" s="1">
         <v>355</v>
-      </c>
-      <c r="O94" s="1">
-        <v>1481</v>
       </c>
       <c r="P94" s="1">
         <v>1481</v>
@@ -5566,8 +5844,11 @@
       <c r="Q94" s="1">
         <v>1481</v>
       </c>
-    </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R94" s="1">
+        <v>1481</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A95" s="6">
         <v>2024</v>
       </c>
@@ -5587,31 +5868,31 @@
         <v>17</v>
       </c>
       <c r="G95" s="1">
+        <v>44</v>
+      </c>
+      <c r="H95" s="1">
         <v>8916</v>
       </c>
-      <c r="H95" s="1">
+      <c r="I95" s="1">
         <v>9900</v>
       </c>
-      <c r="I95" s="1">
+      <c r="J95" s="1">
         <v>55</v>
       </c>
-      <c r="J95" s="1">
+      <c r="K95" s="1">
         <v>22</v>
-      </c>
-      <c r="K95" s="1">
-        <v>33</v>
       </c>
       <c r="L95" s="1">
         <v>33</v>
       </c>
       <c r="M95" s="1">
+        <v>33</v>
+      </c>
+      <c r="N95" s="1">
         <v>22</v>
       </c>
-      <c r="N95" s="1">
+      <c r="O95" s="1">
         <v>264</v>
-      </c>
-      <c r="O95" s="1">
-        <v>1100</v>
       </c>
       <c r="P95" s="1">
         <v>1100</v>
@@ -5619,8 +5900,11 @@
       <c r="Q95" s="1">
         <v>1100</v>
       </c>
-    </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R95" s="1">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="96" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A96" s="6">
         <v>2025</v>
       </c>
@@ -5640,31 +5924,31 @@
         <v>12</v>
       </c>
       <c r="G96" s="1">
+        <v>43</v>
+      </c>
+      <c r="H96" s="1">
         <v>340638</v>
       </c>
-      <c r="H96" s="1">
+      <c r="I96" s="1">
         <v>378486</v>
       </c>
-      <c r="I96" s="1">
+      <c r="J96" s="1">
         <v>2095</v>
       </c>
-      <c r="J96" s="1">
+      <c r="K96" s="1">
         <v>838</v>
-      </c>
-      <c r="K96" s="1">
-        <v>1258</v>
       </c>
       <c r="L96" s="1">
         <v>1258</v>
       </c>
       <c r="M96" s="1">
+        <v>1258</v>
+      </c>
+      <c r="N96" s="1">
         <v>838</v>
       </c>
-      <c r="N96" s="1">
+      <c r="O96" s="1">
         <v>10075</v>
-      </c>
-      <c r="O96" s="1">
-        <v>41980</v>
       </c>
       <c r="P96" s="1">
         <v>41980</v>
@@ -5672,8 +5956,11 @@
       <c r="Q96" s="1">
         <v>41980</v>
       </c>
-    </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R96" s="1">
+        <v>41980</v>
+      </c>
+    </row>
+    <row r="97" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A97" s="6">
         <v>2025</v>
       </c>
@@ -5693,31 +5980,31 @@
         <v>12</v>
       </c>
       <c r="G97" s="1">
+        <v>45</v>
+      </c>
+      <c r="H97" s="1">
         <v>251986</v>
       </c>
-      <c r="H97" s="1">
+      <c r="I97" s="1">
         <v>279984</v>
       </c>
-      <c r="I97" s="1">
+      <c r="J97" s="1">
         <v>1550</v>
       </c>
-      <c r="J97" s="1">
+      <c r="K97" s="1">
         <v>620</v>
-      </c>
-      <c r="K97" s="1">
-        <v>930</v>
       </c>
       <c r="L97" s="1">
         <v>930</v>
       </c>
       <c r="M97" s="1">
+        <v>930</v>
+      </c>
+      <c r="N97" s="1">
         <v>620</v>
       </c>
-      <c r="N97" s="1">
+      <c r="O97" s="1">
         <v>7450</v>
-      </c>
-      <c r="O97" s="1">
-        <v>31044</v>
       </c>
       <c r="P97" s="1">
         <v>31044</v>
@@ -5725,8 +6012,11 @@
       <c r="Q97" s="1">
         <v>31044</v>
       </c>
-    </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R97" s="1">
+        <v>31044</v>
+      </c>
+    </row>
+    <row r="98" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A98" s="6">
         <v>2025</v>
       </c>
@@ -5746,31 +6036,31 @@
         <v>13</v>
       </c>
       <c r="G98" s="1">
+        <v>44</v>
+      </c>
+      <c r="H98" s="1">
         <v>237112</v>
       </c>
-      <c r="H98" s="1">
+      <c r="I98" s="1">
         <v>263346</v>
       </c>
-      <c r="I98" s="1">
+      <c r="J98" s="1">
         <v>1459</v>
       </c>
-      <c r="J98" s="1">
+      <c r="K98" s="1">
         <v>584</v>
-      </c>
-      <c r="K98" s="1">
-        <v>876</v>
       </c>
       <c r="L98" s="1">
         <v>876</v>
       </c>
       <c r="M98" s="1">
+        <v>876</v>
+      </c>
+      <c r="N98" s="1">
         <v>584</v>
       </c>
-      <c r="N98" s="1">
+      <c r="O98" s="1">
         <v>7020</v>
-      </c>
-      <c r="O98" s="1">
-        <v>29210</v>
       </c>
       <c r="P98" s="1">
         <v>29210</v>
@@ -5778,8 +6068,11 @@
       <c r="Q98" s="1">
         <v>29210</v>
       </c>
-    </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R98" s="1">
+        <v>29210</v>
+      </c>
+    </row>
+    <row r="99" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A99" s="6">
         <v>2025</v>
       </c>
@@ -5799,31 +6092,31 @@
         <v>13</v>
       </c>
       <c r="G99" s="1">
+        <v>43</v>
+      </c>
+      <c r="H99" s="1">
         <v>201727</v>
       </c>
-      <c r="H99" s="1">
+      <c r="I99" s="1">
         <v>224112</v>
       </c>
-      <c r="I99" s="1">
+      <c r="J99" s="1">
         <v>1239</v>
       </c>
-      <c r="J99" s="1">
+      <c r="K99" s="1">
         <v>496</v>
-      </c>
-      <c r="K99" s="1">
-        <v>744</v>
       </c>
       <c r="L99" s="1">
         <v>744</v>
       </c>
       <c r="M99" s="1">
+        <v>744</v>
+      </c>
+      <c r="N99" s="1">
         <v>496</v>
       </c>
-      <c r="N99" s="1">
+      <c r="O99" s="1">
         <v>5976</v>
-      </c>
-      <c r="O99" s="1">
-        <v>24850</v>
       </c>
       <c r="P99" s="1">
         <v>24850</v>
@@ -5831,8 +6124,11 @@
       <c r="Q99" s="1">
         <v>24850</v>
       </c>
-    </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R99" s="1">
+        <v>24850</v>
+      </c>
+    </row>
+    <row r="100" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A100" s="6">
         <v>2025</v>
       </c>
@@ -5852,31 +6148,31 @@
         <v>14</v>
       </c>
       <c r="G100" s="1">
+        <v>46</v>
+      </c>
+      <c r="H100" s="1">
         <v>147762</v>
       </c>
-      <c r="H100" s="1">
+      <c r="I100" s="1">
         <v>164208</v>
       </c>
-      <c r="I100" s="1">
+      <c r="J100" s="1">
         <v>909</v>
       </c>
-      <c r="J100" s="1">
+      <c r="K100" s="1">
         <v>364</v>
-      </c>
-      <c r="K100" s="1">
-        <v>546</v>
       </c>
       <c r="L100" s="1">
         <v>546</v>
       </c>
       <c r="M100" s="1">
+        <v>546</v>
+      </c>
+      <c r="N100" s="1">
         <v>364</v>
       </c>
-      <c r="N100" s="1">
+      <c r="O100" s="1">
         <v>4370</v>
-      </c>
-      <c r="O100" s="1">
-        <v>18210</v>
       </c>
       <c r="P100" s="1">
         <v>18210</v>
@@ -5884,8 +6180,11 @@
       <c r="Q100" s="1">
         <v>18210</v>
       </c>
-    </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R100" s="1">
+        <v>18210</v>
+      </c>
+    </row>
+    <row r="101" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A101" s="6">
         <v>2025</v>
       </c>
@@ -5905,31 +6204,31 @@
         <v>13</v>
       </c>
       <c r="G101" s="1">
+        <v>42</v>
+      </c>
+      <c r="H101" s="1">
         <v>143460</v>
       </c>
-      <c r="H101" s="1">
+      <c r="I101" s="1">
         <v>159408</v>
       </c>
-      <c r="I101" s="1">
+      <c r="J101" s="1">
         <v>883</v>
       </c>
-      <c r="J101" s="1">
+      <c r="K101" s="1">
         <v>353</v>
-      </c>
-      <c r="K101" s="1">
-        <v>530</v>
       </c>
       <c r="L101" s="1">
         <v>530</v>
       </c>
       <c r="M101" s="1">
+        <v>530</v>
+      </c>
+      <c r="N101" s="1">
         <v>353</v>
       </c>
-      <c r="N101" s="1">
+      <c r="O101" s="1">
         <v>4243</v>
-      </c>
-      <c r="O101" s="1">
-        <v>17680</v>
       </c>
       <c r="P101" s="1">
         <v>17680</v>
@@ -5937,8 +6236,11 @@
       <c r="Q101" s="1">
         <v>17680</v>
       </c>
-    </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R101" s="1">
+        <v>17680</v>
+      </c>
+    </row>
+    <row r="102" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A102" s="6">
         <v>2025</v>
       </c>
@@ -5958,31 +6260,31 @@
         <v>14</v>
       </c>
       <c r="G102" s="1">
+        <v>47</v>
+      </c>
+      <c r="H102" s="1">
         <v>131358</v>
       </c>
-      <c r="H102" s="1">
+      <c r="I102" s="1">
         <v>145926</v>
       </c>
-      <c r="I102" s="1">
+      <c r="J102" s="1">
         <v>808</v>
       </c>
-      <c r="J102" s="1">
+      <c r="K102" s="1">
         <v>323</v>
-      </c>
-      <c r="K102" s="1">
-        <v>485</v>
       </c>
       <c r="L102" s="1">
         <v>485</v>
       </c>
       <c r="M102" s="1">
+        <v>485</v>
+      </c>
+      <c r="N102" s="1">
         <v>323</v>
       </c>
-      <c r="N102" s="1">
+      <c r="O102" s="1">
         <v>3885</v>
-      </c>
-      <c r="O102" s="1">
-        <v>16190</v>
       </c>
       <c r="P102" s="1">
         <v>16190</v>
@@ -5990,8 +6292,11 @@
       <c r="Q102" s="1">
         <v>16190</v>
       </c>
-    </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R102" s="1">
+        <v>16190</v>
+      </c>
+    </row>
+    <row r="103" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A103" s="6">
         <v>2025</v>
       </c>
@@ -6011,31 +6316,31 @@
         <v>13</v>
       </c>
       <c r="G103" s="1">
+        <v>45</v>
+      </c>
+      <c r="H103" s="1">
         <v>121221</v>
       </c>
-      <c r="H103" s="1">
+      <c r="I103" s="1">
         <v>134664</v>
       </c>
-      <c r="I103" s="1">
+      <c r="J103" s="1">
         <v>746</v>
       </c>
-      <c r="J103" s="1">
+      <c r="K103" s="1">
         <v>299</v>
-      </c>
-      <c r="K103" s="1">
-        <v>447</v>
       </c>
       <c r="L103" s="1">
         <v>447</v>
       </c>
       <c r="M103" s="1">
+        <v>447</v>
+      </c>
+      <c r="N103" s="1">
         <v>299</v>
       </c>
-      <c r="N103" s="1">
+      <c r="O103" s="1">
         <v>3585</v>
-      </c>
-      <c r="O103" s="1">
-        <v>14940</v>
       </c>
       <c r="P103" s="1">
         <v>14940</v>
@@ -6043,8 +6348,11 @@
       <c r="Q103" s="1">
         <v>14940</v>
       </c>
-    </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R103" s="1">
+        <v>14940</v>
+      </c>
+    </row>
+    <row r="104" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A104" s="6">
         <v>2025</v>
       </c>
@@ -6064,31 +6372,31 @@
         <v>12</v>
       </c>
       <c r="G104" s="1">
+        <v>40</v>
+      </c>
+      <c r="H104" s="1">
         <v>118135</v>
       </c>
-      <c r="H104" s="1">
+      <c r="I104" s="1">
         <v>131244</v>
       </c>
-      <c r="I104" s="1">
+      <c r="J104" s="1">
         <v>728</v>
       </c>
-      <c r="J104" s="1">
+      <c r="K104" s="1">
         <v>291</v>
-      </c>
-      <c r="K104" s="1">
-        <v>436</v>
       </c>
       <c r="L104" s="1">
         <v>436</v>
       </c>
       <c r="M104" s="1">
+        <v>436</v>
+      </c>
+      <c r="N104" s="1">
         <v>291</v>
       </c>
-      <c r="N104" s="1">
+      <c r="O104" s="1">
         <v>3495</v>
-      </c>
-      <c r="O104" s="1">
-        <v>14560</v>
       </c>
       <c r="P104" s="1">
         <v>14560</v>
@@ -6096,8 +6404,11 @@
       <c r="Q104" s="1">
         <v>14560</v>
       </c>
-    </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R104" s="1">
+        <v>14560</v>
+      </c>
+    </row>
+    <row r="105" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A105" s="6">
         <v>2025</v>
       </c>
@@ -6117,31 +6428,31 @@
         <v>15</v>
       </c>
       <c r="G105" s="1">
+        <v>38</v>
+      </c>
+      <c r="H105" s="1">
         <v>66540</v>
       </c>
-      <c r="H105" s="1">
+      <c r="I105" s="1">
         <v>73944</v>
       </c>
-      <c r="I105" s="1">
+      <c r="J105" s="1">
         <v>410</v>
       </c>
-      <c r="J105" s="1">
+      <c r="K105" s="1">
         <v>164</v>
-      </c>
-      <c r="K105" s="1">
-        <v>246</v>
       </c>
       <c r="L105" s="1">
         <v>246</v>
       </c>
       <c r="M105" s="1">
+        <v>246</v>
+      </c>
+      <c r="N105" s="1">
         <v>164</v>
       </c>
-      <c r="N105" s="1">
+      <c r="O105" s="1">
         <v>1968</v>
-      </c>
-      <c r="O105" s="1">
-        <v>8200</v>
       </c>
       <c r="P105" s="1">
         <v>8200</v>
@@ -6149,8 +6460,11 @@
       <c r="Q105" s="1">
         <v>8200</v>
       </c>
-    </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R105" s="1">
+        <v>8200</v>
+      </c>
+    </row>
+    <row r="106" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A106" s="6">
         <v>2025</v>
       </c>
@@ -6170,31 +6484,31 @@
         <v>14</v>
       </c>
       <c r="G106" s="1">
+        <v>42</v>
+      </c>
+      <c r="H106" s="1">
         <v>38127</v>
       </c>
-      <c r="H106" s="1">
+      <c r="I106" s="1">
         <v>42363</v>
       </c>
-      <c r="I106" s="1">
+      <c r="J106" s="1">
         <v>235</v>
       </c>
-      <c r="J106" s="1">
+      <c r="K106" s="1">
         <v>94</v>
-      </c>
-      <c r="K106" s="1">
-        <v>141</v>
       </c>
       <c r="L106" s="1">
         <v>141</v>
       </c>
       <c r="M106" s="1">
+        <v>141</v>
+      </c>
+      <c r="N106" s="1">
         <v>94</v>
       </c>
-      <c r="N106" s="1">
+      <c r="O106" s="1">
         <v>1128</v>
-      </c>
-      <c r="O106" s="1">
-        <v>4700</v>
       </c>
       <c r="P106" s="1">
         <v>4700</v>
@@ -6202,8 +6516,11 @@
       <c r="Q106" s="1">
         <v>4700</v>
       </c>
-    </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R106" s="1">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="107" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A107" s="6">
         <v>2025</v>
       </c>
@@ -6223,31 +6540,31 @@
         <v>16</v>
       </c>
       <c r="G107" s="1">
+        <v>44</v>
+      </c>
+      <c r="H107" s="1">
         <v>13389</v>
       </c>
-      <c r="H107" s="1">
+      <c r="I107" s="1">
         <v>14874</v>
       </c>
-      <c r="I107" s="1">
+      <c r="J107" s="1">
         <v>82</v>
       </c>
-      <c r="J107" s="1">
+      <c r="K107" s="1">
         <v>33</v>
-      </c>
-      <c r="K107" s="1">
-        <v>50</v>
       </c>
       <c r="L107" s="1">
         <v>50</v>
       </c>
       <c r="M107" s="1">
+        <v>50</v>
+      </c>
+      <c r="N107" s="1">
         <v>33</v>
       </c>
-      <c r="N107" s="1">
+      <c r="O107" s="1">
         <v>405</v>
-      </c>
-      <c r="O107" s="1">
-        <v>1650</v>
       </c>
       <c r="P107" s="1">
         <v>1650</v>
@@ -6255,8 +6572,11 @@
       <c r="Q107" s="1">
         <v>1650</v>
       </c>
-    </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R107" s="1">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="108" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A108" s="6">
         <v>2025</v>
       </c>
@@ -6275,32 +6595,30 @@
       <c r="F108" s="1">
         <v>16</v>
       </c>
-      <c r="G108" s="1">
+      <c r="G108" s="1"/>
+      <c r="H108" s="1">
         <v>12162</v>
       </c>
-      <c r="H108" s="1">
+      <c r="I108" s="1">
         <v>13512</v>
       </c>
-      <c r="I108" s="1">
+      <c r="J108" s="1">
         <v>75</v>
       </c>
-      <c r="J108" s="1">
+      <c r="K108" s="1">
         <v>30</v>
-      </c>
-      <c r="K108" s="1">
-        <v>45</v>
       </c>
       <c r="L108" s="1">
         <v>45</v>
       </c>
       <c r="M108" s="1">
+        <v>45</v>
+      </c>
+      <c r="N108" s="1">
         <v>30</v>
       </c>
-      <c r="N108" s="1">
+      <c r="O108" s="1">
         <v>360</v>
-      </c>
-      <c r="O108" s="1">
-        <v>1500</v>
       </c>
       <c r="P108" s="1">
         <v>1500</v>
@@ -6308,8 +6626,11 @@
       <c r="Q108" s="1">
         <v>1500</v>
       </c>
-    </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="R108" s="1">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
         <v>46</v>
       </c>
@@ -6321,8 +6642,9 @@
       <c r="G115" s="3"/>
       <c r="H115" s="3"/>
       <c r="I115" s="3"/>
-    </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J115" s="3"/>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" s="3" t="s">
         <v>47</v>
       </c>
@@ -6334,8 +6656,9 @@
       <c r="G116" s="3"/>
       <c r="H116" s="3"/>
       <c r="I116" s="3"/>
-    </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J116" s="3"/>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
         <v>48</v>
       </c>
@@ -6347,8 +6670,9 @@
       <c r="G117" s="3"/>
       <c r="H117" s="3"/>
       <c r="I117" s="3"/>
-    </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J117" s="3"/>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="s">
         <v>49</v>
       </c>
@@ -6360,6 +6684,7 @@
       <c r="G118" s="3"/>
       <c r="H118" s="3"/>
       <c r="I118" s="3"/>
+      <c r="J118" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/modules/resource_recommendation/data/Gampaha_DS_Flood_Emergency_Relief_2019_2025.xlsx
+++ b/modules/resource_recommendation/data/Gampaha_DS_Flood_Emergency_Relief_2019_2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lap.lk\Desktop\UOM\Year 4\Sem 1\Research\Flood-Relief-Mapping\modules\resource_recommendation\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3D869EA-E351-4C97-8C8B-594A311EB744}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63E0FFC1-0C68-4DBE-AF52-C7D4F433D159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6595,7 +6595,9 @@
       <c r="F108" s="1">
         <v>16</v>
       </c>
-      <c r="G108" s="1"/>
+      <c r="G108" s="1">
+        <v>39</v>
+      </c>
       <c r="H108" s="1">
         <v>12162</v>
       </c>
